--- a/카드_아키타입/10_세정(클렌징).xlsx
+++ b/카드_아키타입/10_세정(클렌징).xlsx
@@ -1256,7 +1256,7 @@
       <row>93</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="43" name="Image 43" descr="Picture"/>
@@ -4031,7 +4031,7 @@
       <row>268</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1038225"/>
+    <ext cx="1047750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="154" name="Image 154" descr="Picture"/>

--- a/카드_아키타입/10_세정(클렌징).xlsx
+++ b/카드_아키타입/10_세정(클렌징).xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="8013700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="8013700"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="8013700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="8013700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="9861550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>11</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="9861550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>11</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="9861550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>11</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="9861550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="15417800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="15417800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="15417800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="15417800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="23431500"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="28219400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="28219400"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="28219400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="28219400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="30067250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>54</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="38468300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>54</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="38468300"/>
     <ext cx="1809750" cy="838200"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>54</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="38468300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>54</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="38468300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>54</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="40316149"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>54</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="40316149"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>54</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="40316149"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>54</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="40316149"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>54</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="42163999"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>54</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="42163999"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>54</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="42163999"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>54</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="42163999"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>54</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="44011849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>54</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="44011849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>54</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="44011849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>54</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="44011849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>54</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="45859699"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>70</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="53390800"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>70</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="53390800"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>70</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="53390800"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>70</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="53390800"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>70</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="55238650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>70</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="55238650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>70</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="55238650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>70</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="55238650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>82</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="58153300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>82</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="58153300"/>
     <ext cx="1028700" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>82</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="58153300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>82</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="58153300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>82</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="60001150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>82</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="60001150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>82</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="60001150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>82</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="60001150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>94</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="69418200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>94</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="69418200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>94</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="69418200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>94</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="69418200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>94</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="71266050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>94</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="71266050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>94</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="71266050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>94</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="71266050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>94</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="73113900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>94</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="73113900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>104</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="77635100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>104</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="77635100"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>104</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="77635100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>104</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="77635100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>104</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="79482950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>104</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="79482950"/>
     <ext cx="1809750" cy="1438275"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>117</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="86055200"/>
     <ext cx="1695450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>117</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="86055200"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>117</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="86055200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>117</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="86055200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>117</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="87903050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>117</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="87903050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>117</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="87903050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>117</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="87903050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>128</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="97929700"/>
     <ext cx="1200150" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>128</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="97929700"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>128</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="97929700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>128</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="97929700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>128</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="99777550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>140</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="107772200"/>
     <ext cx="1295400" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>140</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="107772200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>140</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="107772200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>140</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="107772200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>140</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="109620050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2498,14 +2038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>140</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="109620050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2523,14 +2058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>140</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="109620050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2548,14 +2078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>140</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="109620050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2573,14 +2098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>140</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="111467900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2598,14 +2118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>140</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="111467900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2623,14 +2138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>140</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="111467900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2648,14 +2158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="119037100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2673,14 +2178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="119037100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2698,14 +2198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="119037100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2723,14 +2218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="119037100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2748,14 +2238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="120884950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2773,14 +2258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="120884950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2798,14 +2278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="120884950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2823,14 +2298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>162</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="126847600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2848,14 +2318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>162</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="126847600"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -2873,14 +2338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>162</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="126847600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2898,14 +2358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>162</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="126847600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2923,14 +2378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>162</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="128695450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2948,14 +2398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>162</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="128695450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2973,14 +2418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>162</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="128695450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2998,14 +2438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>173</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="133642100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3023,14 +2458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>173</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="133642100"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3048,14 +2478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>173</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="133642100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -3073,14 +2498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>173</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="133642100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3098,14 +2518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>173</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="135489950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3123,14 +2538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>173</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="135489950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3148,14 +2558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>173</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="135489950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3173,14 +2578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>173</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="135489950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3198,14 +2598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>173</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="137337800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3223,14 +2618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>183</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="141249400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3248,14 +2638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>183</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="141249400"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3273,14 +2658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>183</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="141249400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3298,14 +2678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>183</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="141249400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3323,14 +2698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>183</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="143097250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3348,14 +2718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>183</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="143097250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3373,14 +2738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>183</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="143097250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3398,14 +2758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>183</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="143097250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3423,14 +2778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="148043900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3448,14 +2798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="148043900"/>
     <ext cx="1809750" cy="1314450"/>
     <pic>
       <nvPicPr>
@@ -3473,14 +2818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="148043900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3498,14 +2838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="148043900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3523,14 +2858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="149891750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3548,14 +2878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>195</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="149891750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3573,14 +2898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>195</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="149891750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3598,14 +2918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>195</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="149891750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3623,14 +2938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>207</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="155041600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3648,14 +2958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>207</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="155041600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3673,14 +2978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>207</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="155041600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3698,14 +2998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>207</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="155041600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3723,14 +3018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>207</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="156889450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3748,14 +3038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>207</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="156889450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3773,14 +3058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>207</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="156889450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3798,14 +3078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>207</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="156889450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3823,14 +3098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>207</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="158737300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3848,14 +3118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>207</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="158737300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3873,14 +3138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>207</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="158737300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3898,14 +3158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>207</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="158737300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3923,14 +3178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>207</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="160585150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3948,14 +3198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>207</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="160585150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3973,14 +3218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>224</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="166916100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3998,14 +3238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>224</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="166916100"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4023,14 +3258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>224</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="166916100"/>
     <ext cx="1809750" cy="1781175"/>
     <pic>
       <nvPicPr>
@@ -4048,14 +3278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>224</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="166916100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4073,14 +3298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>224</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="168763950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4098,14 +3318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>224</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="168763950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4123,14 +3338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>224</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="168763950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4148,14 +3358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>224</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="168763950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4173,14 +3378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>224</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="170611800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4198,14 +3398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>235</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="175133000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4223,14 +3418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>235</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="175133000"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4248,14 +3438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>235</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="175133000"/>
     <ext cx="1809750" cy="676275"/>
     <pic>
       <nvPicPr>
@@ -4273,14 +3458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>235</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="175133000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4298,14 +3478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>235</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="176980850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4323,14 +3498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>235</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="176980850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4348,14 +3518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>235</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="176980850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4373,14 +3538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>235</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="176980850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4398,14 +3558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>235</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="178828700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4423,14 +3578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>247</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="181927500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4448,14 +3598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>247</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="181927500"/>
     <ext cx="1685925" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4473,14 +3618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>247</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="181927500"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -4498,14 +3638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>247</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="181927500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4523,14 +3658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>247</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="183775350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4548,14 +3678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>247</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="183775350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4573,14 +3698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>247</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="183775350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4598,14 +3718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>247</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="183775350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4623,14 +3738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>247</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="185623200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4648,14 +3758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>257</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="188112400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4673,14 +3778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>257</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="188112400"/>
     <ext cx="1609725" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4698,14 +3798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>257</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="188112400"/>
     <ext cx="1809750" cy="676275"/>
     <pic>
       <nvPicPr>
@@ -4723,14 +3818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>257</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="188112400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4748,14 +3838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>257</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="189960250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4773,14 +3858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>257</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="189960250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4798,14 +3878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>257</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="189960250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4823,14 +3898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>257</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="189960250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4848,14 +3918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>257</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="191808100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4873,14 +3938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>268</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="194500500"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4898,14 +3958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>268</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="194500500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4923,14 +3978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>268</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="194500500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4948,14 +3998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>268</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="194500500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4973,14 +4018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>268</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="196348350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4998,14 +4038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>268</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="196348350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5023,14 +4058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>279</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="201498200"/>
     <ext cx="1314450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5048,14 +4078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>279</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="201498200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5073,14 +4098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>279</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="201498200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5098,14 +4118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>279</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="201498200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5123,14 +4138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>279</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="203346050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5148,14 +4158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>279</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="203346050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5173,14 +4178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>279</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="203346050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5198,14 +4198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>279</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="203346050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5223,14 +4218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>279</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="205193900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5248,14 +4238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>297</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="215404700"/>
     <ext cx="1657350" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5273,14 +4258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>297</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="215404700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5298,14 +4278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>297</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="215404700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5323,14 +4298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>297</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="215404700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5348,14 +4318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>297</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="217252550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5373,14 +4338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>297</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="217252550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5398,14 +4358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>297</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="217252550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5423,14 +4378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>308</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="222808800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5448,14 +4398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>308</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="222808800"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -5473,14 +4418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>308</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="222808800"/>
     <ext cx="1809750" cy="809625"/>
     <pic>
       <nvPicPr>
@@ -5498,14 +4438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>308</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="222808800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5523,14 +4458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>308</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="224656650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5548,14 +4478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>308</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="224656650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5573,14 +4498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>319</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="228587300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5598,14 +4518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>319</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="228587300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5623,14 +4538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>319</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="228587300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5648,14 +4558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>319</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="228587300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5673,14 +4578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>335</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="238226600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5698,14 +4598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>335</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="238226600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5723,14 +4618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>335</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="238226600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5748,14 +4638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>335</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="238226600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5773,14 +4658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="248069100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5798,14 +4678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="248069100"/>
     <ext cx="1552575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5823,14 +4698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="248069100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -5848,14 +4718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="248069100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5873,14 +4738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>349</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="249916950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5898,14 +4758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>349</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="249916950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5923,14 +4778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>349</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="249916950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5948,14 +4798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>349</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="249916950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5973,14 +4818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>349</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="251764800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5998,14 +4838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>349</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="251764800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6023,14 +4858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>349</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="251764800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6048,14 +4878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>349</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="251764800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6073,14 +4898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>359</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="256489200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6098,14 +4918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>359</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="256489200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6123,14 +4938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>359</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="256489200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6148,14 +4958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>359</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="256489200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6173,14 +4978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>374</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="264096500"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -6198,14 +4998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>374</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="264096500"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -6223,14 +5018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>386</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="269468600"/>
     <ext cx="1809750" cy="1219200"/>
     <pic>
       <nvPicPr>
@@ -6248,14 +5038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>386</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="269468600"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -6273,14 +5058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>386</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="269468600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6298,14 +5078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>386</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="269468600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6323,14 +5098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>386</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="271316450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6348,14 +5118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>398</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="279717500"/>
     <ext cx="1447800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6373,14 +5138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>398</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="279717500"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6398,14 +5158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>398</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="279717500"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6423,14 +5178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>398</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="279717500"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6448,14 +5198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>398</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="281565350"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6473,14 +5218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>411</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="286105600"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -6498,14 +5238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>411</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="286105600"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -6523,14 +5258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>411</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="286105600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6548,14 +5278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>411</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="286105600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6573,14 +5298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>411</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="287953450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6598,14 +5318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>411</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="287953450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6623,14 +5338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>411</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="287953450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6648,14 +5358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>411</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="287953450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6673,14 +5378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>411</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="289801300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6698,14 +5398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>411</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="289801300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6723,14 +5418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>411</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="289801300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6748,14 +5438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="294525700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6773,14 +5458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="294525700"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -6798,14 +5478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="294525700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6823,14 +5498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="294525700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6848,14 +5518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>421</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="296373550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6873,14 +5538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>421</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="296373550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6898,14 +5558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>421</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="296373550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6923,14 +5578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>421</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="296373550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6948,14 +5598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>436</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="302336200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6973,14 +5618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>436</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="302336200"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -6998,14 +5638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>436</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="302336200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7023,14 +5658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>436</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="302336200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7048,14 +5678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>436</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="304184050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7073,14 +5698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>436</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="304184050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7098,14 +5718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>436</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="304184050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7123,14 +5738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>436</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="304184050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7148,14 +5758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>451</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="310553100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7173,14 +5778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>451</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="310553100"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7198,14 +5798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>451</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="310553100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7223,14 +5818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>451</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="310553100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7248,14 +5838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>451</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="312400950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7273,14 +5858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>451</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="312400950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7298,14 +5878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>451</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="312400950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7323,14 +5898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>451</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="312400950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7348,14 +5918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>451</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="314248800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7373,14 +5938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>451</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="314248800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7398,14 +5958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>451</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="314248800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7423,14 +5978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>451</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="314248800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7448,14 +5998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>451</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="316096650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7473,14 +6018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>463</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="321614800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7498,14 +6038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>463</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="321614800"/>
     <ext cx="1809750" cy="1466850"/>
     <pic>
       <nvPicPr>
@@ -7523,14 +6058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>463</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="321614800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7548,14 +6078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>463</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="321614800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7573,14 +6098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>463</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="323462650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7598,14 +6118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>463</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="323462650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7623,14 +6138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>463</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="323462650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7648,14 +6158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>463</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="323462650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7673,14 +6178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>463</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="325310500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7698,14 +6198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>463</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="325310500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7723,14 +6218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>477</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="332473300"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7748,14 +6238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>491</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="339064600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7773,14 +6258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>491</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="339064600"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -7798,14 +6278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>491</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="339064600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7823,14 +6298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>491</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="339064600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7848,14 +6318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>491</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="340912450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7873,14 +6338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>502</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="344233500"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7898,14 +6358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>516</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="351231200"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7923,14 +6378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>527</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="356831900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7948,14 +6398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>527</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="356831900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7973,14 +6418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>527</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="356831900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7998,14 +6438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>527</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="356831900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8023,14 +6458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>527</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="358679750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8048,14 +6478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>527</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="358679750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8073,14 +6498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>527</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="358679750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8098,14 +6518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>536</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="363626400"/>
     <ext cx="1190625" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8123,14 +6538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>547</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="369811300"/>
     <ext cx="1143000" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8148,14 +6558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>559</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="376834400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -8173,14 +6578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>559</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="376834400"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -8198,14 +6598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>559</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="376834400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8223,14 +6618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>559</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="376834400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8248,14 +6638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>559</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="378682250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8273,14 +6658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>575</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="389724900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8298,14 +6678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>575</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="389724900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8323,14 +6698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>575</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="389724900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8348,14 +6718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>575</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="389724900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8373,14 +6738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>575</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="391572750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8398,14 +6758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>575</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="391572750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8423,14 +6778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>575</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="391572750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8448,14 +6798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>586</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="397535400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8473,14 +6818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>586</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="397535400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8498,14 +6838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>586</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="397535400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8523,14 +6858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>586</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="397535400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8548,7 +6878,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/10_세정(클렌징).xlsx
+++ b/카드_아키타입/10_세정(클렌징).xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="0"/>
+    <pos x="9239250" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="0"/>
+    <pos x="11087100" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="0"/>
+    <pos x="12934950" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="1847850"/>
+    <pos x="7391400" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="1847850"/>
+    <pos x="9239250" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="1847850"/>
+    <pos x="11087100" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="8013700"/>
+    <pos x="7391400" y="8013700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="8013700"/>
+    <pos x="9239250" y="8013700"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="8013700"/>
+    <pos x="11087100" y="8013700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="8013700"/>
+    <pos x="12934950" y="8013700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="9861550"/>
+    <pos x="7391400" y="9861550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="9861550"/>
+    <pos x="9239250" y="9861550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="9861550"/>
+    <pos x="11087100" y="9861550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="9861550"/>
+    <pos x="12934950" y="9861550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="15417800"/>
+    <pos x="7391400" y="15417800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="15417800"/>
+    <pos x="9239250" y="15417800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="15417800"/>
+    <pos x="11087100" y="15417800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="15417800"/>
+    <pos x="12934950" y="15417800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="23431500"/>
+    <pos x="7391400" y="23431500"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="28219400"/>
+    <pos x="7391400" y="28219400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="28219400"/>
+    <pos x="9239250" y="28219400"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="28219400"/>
+    <pos x="11087100" y="28219400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="28219400"/>
+    <pos x="12934950" y="28219400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="30067250"/>
+    <pos x="7391400" y="30067250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="38468300"/>
+    <pos x="7391400" y="38468300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="38468300"/>
+    <pos x="9239250" y="38468300"/>
     <ext cx="1809750" cy="838200"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="38468300"/>
+    <pos x="11087100" y="38468300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="38468300"/>
+    <pos x="12934950" y="38468300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="40316149"/>
+    <pos x="7391400" y="40316149"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="40316149"/>
+    <pos x="9239250" y="40316149"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="40316149"/>
+    <pos x="11087100" y="40316149"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="40316149"/>
+    <pos x="12934950" y="40316149"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="42163999"/>
+    <pos x="7391400" y="42163999"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="42163999"/>
+    <pos x="9239250" y="42163999"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="42163999"/>
+    <pos x="11087100" y="42163999"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="42163999"/>
+    <pos x="12934950" y="42163999"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="44011849"/>
+    <pos x="7391400" y="44011849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="44011849"/>
+    <pos x="9239250" y="44011849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="44011849"/>
+    <pos x="11087100" y="44011849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="44011849"/>
+    <pos x="12934950" y="44011849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="45859699"/>
+    <pos x="7391400" y="45859699"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="53390800"/>
+    <pos x="7391400" y="53390800"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="53390800"/>
+    <pos x="9239250" y="53390800"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="53390800"/>
+    <pos x="11087100" y="53390800"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="53390800"/>
+    <pos x="12934950" y="53390800"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="55238650"/>
+    <pos x="7391400" y="55238650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="55238650"/>
+    <pos x="9239250" y="55238650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="55238650"/>
+    <pos x="11087100" y="55238650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="55238650"/>
+    <pos x="12934950" y="55238650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="58153300"/>
+    <pos x="7391400" y="58153300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="58153300"/>
+    <pos x="9239250" y="58153300"/>
     <ext cx="1028700" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="58153300"/>
+    <pos x="11087100" y="58153300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="58153300"/>
+    <pos x="12934950" y="58153300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="60001150"/>
+    <pos x="7391400" y="60001150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="60001150"/>
+    <pos x="9239250" y="60001150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="60001150"/>
+    <pos x="11087100" y="60001150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="60001150"/>
+    <pos x="12934950" y="60001150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="69418200"/>
+    <pos x="7391400" y="69418200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="69418200"/>
+    <pos x="9239250" y="69418200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="69418200"/>
+    <pos x="11087100" y="69418200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="69418200"/>
+    <pos x="12934950" y="69418200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="71266050"/>
+    <pos x="7391400" y="71266050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="71266050"/>
+    <pos x="9239250" y="71266050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="71266050"/>
+    <pos x="11087100" y="71266050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="71266050"/>
+    <pos x="12934950" y="71266050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="73113900"/>
+    <pos x="7391400" y="73113900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="73113900"/>
+    <pos x="9239250" y="73113900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="77635100"/>
+    <pos x="7391400" y="77635100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="77635100"/>
+    <pos x="9239250" y="77635100"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="77635100"/>
+    <pos x="11087100" y="77635100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="77635100"/>
+    <pos x="12934950" y="77635100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="79482950"/>
+    <pos x="7391400" y="79482950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="79482950"/>
+    <pos x="9239250" y="79482950"/>
     <ext cx="1809750" cy="1438275"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="86055200"/>
+    <pos x="7391400" y="86055200"/>
     <ext cx="1695450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="86055200"/>
+    <pos x="9239250" y="86055200"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="86055200"/>
+    <pos x="11087100" y="86055200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="86055200"/>
+    <pos x="12934950" y="86055200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="87903050"/>
+    <pos x="7391400" y="87903050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="87903050"/>
+    <pos x="9239250" y="87903050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="87903050"/>
+    <pos x="11087100" y="87903050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="87903050"/>
+    <pos x="12934950" y="87903050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="97929700"/>
+    <pos x="7391400" y="97929700"/>
     <ext cx="1200150" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="97929700"/>
+    <pos x="9239250" y="97929700"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="97929700"/>
+    <pos x="11087100" y="97929700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="97929700"/>
+    <pos x="12934950" y="97929700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="99777550"/>
+    <pos x="7391400" y="99777550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="107772200"/>
+    <pos x="7391400" y="107772200"/>
     <ext cx="1295400" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="107772200"/>
+    <pos x="9239250" y="107772200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="107772200"/>
+    <pos x="11087100" y="107772200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="107772200"/>
+    <pos x="12934950" y="107772200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="109620050"/>
+    <pos x="7391400" y="109620050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="109620050"/>
+    <pos x="9239250" y="109620050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="109620050"/>
+    <pos x="11087100" y="109620050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="109620050"/>
+    <pos x="12934950" y="109620050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="111467900"/>
+    <pos x="7391400" y="111467900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="111467900"/>
+    <pos x="9239250" y="111467900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="111467900"/>
+    <pos x="11087100" y="111467900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="119037100"/>
+    <pos x="7391400" y="119037100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="119037100"/>
+    <pos x="9239250" y="119037100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="119037100"/>
+    <pos x="11087100" y="119037100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="119037100"/>
+    <pos x="12934950" y="119037100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="120884950"/>
+    <pos x="7391400" y="120884950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="120884950"/>
+    <pos x="9239250" y="120884950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="120884950"/>
+    <pos x="11087100" y="120884950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="126847600"/>
+    <pos x="7391400" y="126847600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="126847600"/>
+    <pos x="9239250" y="126847600"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="126847600"/>
+    <pos x="11087100" y="126847600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="126847600"/>
+    <pos x="12934950" y="126847600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="128695450"/>
+    <pos x="7391400" y="128695450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="128695450"/>
+    <pos x="9239250" y="128695450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="128695450"/>
+    <pos x="11087100" y="128695450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="133642100"/>
+    <pos x="7391400" y="133642100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="133642100"/>
+    <pos x="9239250" y="133642100"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="133642100"/>
+    <pos x="11087100" y="133642100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="133642100"/>
+    <pos x="12934950" y="133642100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="135489950"/>
+    <pos x="7391400" y="135489950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="135489950"/>
+    <pos x="9239250" y="135489950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="135489950"/>
+    <pos x="11087100" y="135489950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="135489950"/>
+    <pos x="12934950" y="135489950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="137337800"/>
+    <pos x="7391400" y="137337800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="141249400"/>
+    <pos x="7391400" y="141249400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="141249400"/>
+    <pos x="9239250" y="141249400"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="141249400"/>
+    <pos x="11087100" y="141249400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="141249400"/>
+    <pos x="12934950" y="141249400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="143097250"/>
+    <pos x="7391400" y="143097250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="143097250"/>
+    <pos x="9239250" y="143097250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="143097250"/>
+    <pos x="11087100" y="143097250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="143097250"/>
+    <pos x="12934950" y="143097250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="148043900"/>
+    <pos x="7391400" y="148043900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="148043900"/>
+    <pos x="9239250" y="148043900"/>
     <ext cx="1809750" cy="1314450"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="148043900"/>
+    <pos x="11087100" y="148043900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="148043900"/>
+    <pos x="12934950" y="148043900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="149891750"/>
+    <pos x="7391400" y="149891750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="149891750"/>
+    <pos x="9239250" y="149891750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +2900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="149891750"/>
+    <pos x="11087100" y="149891750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +2920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="149891750"/>
+    <pos x="12934950" y="149891750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +2940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="155041600"/>
+    <pos x="7391400" y="155041600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +2960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="155041600"/>
+    <pos x="9239250" y="155041600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +2980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="155041600"/>
+    <pos x="11087100" y="155041600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="155041600"/>
+    <pos x="12934950" y="155041600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="156889450"/>
+    <pos x="7391400" y="156889450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="156889450"/>
+    <pos x="9239250" y="156889450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="156889450"/>
+    <pos x="11087100" y="156889450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="156889450"/>
+    <pos x="12934950" y="156889450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="158737300"/>
+    <pos x="7391400" y="158737300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="158737300"/>
+    <pos x="9239250" y="158737300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="158737300"/>
+    <pos x="11087100" y="158737300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="158737300"/>
+    <pos x="12934950" y="158737300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="160585150"/>
+    <pos x="7391400" y="160585150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="160585150"/>
+    <pos x="9239250" y="160585150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="166916100"/>
+    <pos x="7391400" y="166916100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="166916100"/>
+    <pos x="9239250" y="166916100"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="166916100"/>
+    <pos x="11087100" y="166916100"/>
     <ext cx="1809750" cy="1781175"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="166916100"/>
+    <pos x="12934950" y="166916100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="168763950"/>
+    <pos x="7391400" y="168763950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="168763950"/>
+    <pos x="9239250" y="168763950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="168763950"/>
+    <pos x="11087100" y="168763950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="168763950"/>
+    <pos x="12934950" y="168763950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="170611800"/>
+    <pos x="7391400" y="170611800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3400,7 +3400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="175133000"/>
+    <pos x="7391400" y="175133000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3420,7 +3420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="175133000"/>
+    <pos x="9239250" y="175133000"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="175133000"/>
+    <pos x="11087100" y="175133000"/>
     <ext cx="1809750" cy="676275"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="175133000"/>
+    <pos x="12934950" y="175133000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="176980850"/>
+    <pos x="7391400" y="176980850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="176980850"/>
+    <pos x="9239250" y="176980850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="176980850"/>
+    <pos x="11087100" y="176980850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="176980850"/>
+    <pos x="12934950" y="176980850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="178828700"/>
+    <pos x="7391400" y="178828700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="181927500"/>
+    <pos x="7391400" y="181927500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3600,7 +3600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="181927500"/>
+    <pos x="9239250" y="181927500"/>
     <ext cx="1685925" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3620,7 +3620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="181927500"/>
+    <pos x="11087100" y="181927500"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -3640,7 +3640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="181927500"/>
+    <pos x="12934950" y="181927500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3660,7 +3660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="183775350"/>
+    <pos x="7391400" y="183775350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3680,7 +3680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="183775350"/>
+    <pos x="9239250" y="183775350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3700,7 +3700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="183775350"/>
+    <pos x="11087100" y="183775350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3720,7 +3720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="183775350"/>
+    <pos x="12934950" y="183775350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3740,7 +3740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="185623200"/>
+    <pos x="7391400" y="185623200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3760,7 +3760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="188112400"/>
+    <pos x="7391400" y="188112400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3780,7 +3780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="188112400"/>
+    <pos x="9239250" y="188112400"/>
     <ext cx="1609725" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3800,7 +3800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="188112400"/>
+    <pos x="11087100" y="188112400"/>
     <ext cx="1809750" cy="676275"/>
     <pic>
       <nvPicPr>
@@ -3820,7 +3820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="188112400"/>
+    <pos x="12934950" y="188112400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3840,7 +3840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="189960250"/>
+    <pos x="7391400" y="189960250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3860,7 +3860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="189960250"/>
+    <pos x="9239250" y="189960250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3880,7 +3880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="189960250"/>
+    <pos x="11087100" y="189960250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3900,7 +3900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="189960250"/>
+    <pos x="12934950" y="189960250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3920,7 +3920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="191808100"/>
+    <pos x="7391400" y="191808100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3940,7 +3940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="194500500"/>
+    <pos x="7391400" y="194500500"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3960,7 +3960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="194500500"/>
+    <pos x="9239250" y="194500500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3980,7 +3980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="194500500"/>
+    <pos x="11087100" y="194500500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4000,7 +4000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="194500500"/>
+    <pos x="12934950" y="194500500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4020,7 +4020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="196348350"/>
+    <pos x="7391400" y="196348350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4040,7 +4040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="196348350"/>
+    <pos x="9239250" y="196348350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4060,7 +4060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="201498200"/>
+    <pos x="7391400" y="201498200"/>
     <ext cx="1314450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4080,7 +4080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="201498200"/>
+    <pos x="9239250" y="201498200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4100,7 +4100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="201498200"/>
+    <pos x="11087100" y="201498200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4120,7 +4120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="201498200"/>
+    <pos x="12934950" y="201498200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4140,7 +4140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="203346050"/>
+    <pos x="7391400" y="203346050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4160,7 +4160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="203346050"/>
+    <pos x="9239250" y="203346050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4180,7 +4180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="203346050"/>
+    <pos x="11087100" y="203346050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4200,7 +4200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="203346050"/>
+    <pos x="12934950" y="203346050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4220,7 +4220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="205193900"/>
+    <pos x="7391400" y="205193900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4240,7 +4240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="215404700"/>
+    <pos x="7391400" y="215404700"/>
     <ext cx="1657350" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4260,7 +4260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="215404700"/>
+    <pos x="9239250" y="215404700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4280,7 +4280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="215404700"/>
+    <pos x="11087100" y="215404700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4300,7 +4300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="215404700"/>
+    <pos x="12934950" y="215404700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4320,7 +4320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="217252550"/>
+    <pos x="7391400" y="217252550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4340,7 +4340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="217252550"/>
+    <pos x="9239250" y="217252550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4360,7 +4360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="217252550"/>
+    <pos x="11087100" y="217252550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4380,7 +4380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="222808800"/>
+    <pos x="7391400" y="222808800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4400,7 +4400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="222808800"/>
+    <pos x="9239250" y="222808800"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -4420,7 +4420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="222808800"/>
+    <pos x="11087100" y="222808800"/>
     <ext cx="1809750" cy="809625"/>
     <pic>
       <nvPicPr>
@@ -4440,7 +4440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="222808800"/>
+    <pos x="12934950" y="222808800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4460,7 +4460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="224656650"/>
+    <pos x="7391400" y="224656650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4480,7 +4480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="224656650"/>
+    <pos x="9239250" y="224656650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4500,7 +4500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="228587300"/>
+    <pos x="7391400" y="228587300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4520,7 +4520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="228587300"/>
+    <pos x="9239250" y="228587300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4540,7 +4540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="228587300"/>
+    <pos x="11087100" y="228587300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4560,7 +4560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="228587300"/>
+    <pos x="12934950" y="228587300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4580,7 +4580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="238226600"/>
+    <pos x="7391400" y="238226600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4600,7 +4600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="238226600"/>
+    <pos x="9239250" y="238226600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4620,7 +4620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="238226600"/>
+    <pos x="11087100" y="238226600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4640,7 +4640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="238226600"/>
+    <pos x="12934950" y="238226600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4660,7 +4660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="248069100"/>
+    <pos x="7391400" y="248069100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4680,7 +4680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="248069100"/>
+    <pos x="9239250" y="248069100"/>
     <ext cx="1552575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4700,7 +4700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="248069100"/>
+    <pos x="11087100" y="248069100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -4720,7 +4720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="248069100"/>
+    <pos x="12934950" y="248069100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4740,7 +4740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="249916950"/>
+    <pos x="7391400" y="249916950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4760,7 +4760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="249916950"/>
+    <pos x="9239250" y="249916950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4780,7 +4780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="249916950"/>
+    <pos x="11087100" y="249916950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4800,7 +4800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="249916950"/>
+    <pos x="12934950" y="249916950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4820,7 +4820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="251764800"/>
+    <pos x="7391400" y="251764800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4840,7 +4840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="251764800"/>
+    <pos x="9239250" y="251764800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4860,7 +4860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="251764800"/>
+    <pos x="11087100" y="251764800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4880,7 +4880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="251764800"/>
+    <pos x="12934950" y="251764800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4900,7 +4900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="256489200"/>
+    <pos x="7391400" y="256489200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4920,7 +4920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="256489200"/>
+    <pos x="9239250" y="256489200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4940,7 +4940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="256489200"/>
+    <pos x="11087100" y="256489200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4960,7 +4960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="256489200"/>
+    <pos x="12934950" y="256489200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4980,7 +4980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="264096500"/>
+    <pos x="7391400" y="264096500"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -5000,7 +5000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="264096500"/>
+    <pos x="9239250" y="264096500"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -5020,7 +5020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="269468600"/>
+    <pos x="7391400" y="269468600"/>
     <ext cx="1809750" cy="1219200"/>
     <pic>
       <nvPicPr>
@@ -5040,7 +5040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="269468600"/>
+    <pos x="9239250" y="269468600"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -5060,7 +5060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="269468600"/>
+    <pos x="11087100" y="269468600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5080,7 +5080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="269468600"/>
+    <pos x="12934950" y="269468600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5100,7 +5100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="271316450"/>
+    <pos x="7391400" y="271316450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5120,7 +5120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="279717500"/>
+    <pos x="7391400" y="279717500"/>
     <ext cx="1447800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5140,7 +5140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="279717500"/>
+    <pos x="9239250" y="279717500"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5160,7 +5160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="279717500"/>
+    <pos x="11087100" y="279717500"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5180,7 +5180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="279717500"/>
+    <pos x="12934950" y="279717500"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5200,7 +5200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="281565350"/>
+    <pos x="7391400" y="281565350"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5220,7 +5220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="286105600"/>
+    <pos x="7391400" y="286105600"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -5240,7 +5240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="286105600"/>
+    <pos x="9239250" y="286105600"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -5260,7 +5260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="286105600"/>
+    <pos x="11087100" y="286105600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5280,7 +5280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="286105600"/>
+    <pos x="12934950" y="286105600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5300,7 +5300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="287953450"/>
+    <pos x="7391400" y="287953450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5320,7 +5320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="287953450"/>
+    <pos x="9239250" y="287953450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5340,7 +5340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="287953450"/>
+    <pos x="11087100" y="287953450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5360,7 +5360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="287953450"/>
+    <pos x="12934950" y="287953450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5380,7 +5380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="289801300"/>
+    <pos x="7391400" y="289801300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5400,7 +5400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="289801300"/>
+    <pos x="9239250" y="289801300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5420,7 +5420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="289801300"/>
+    <pos x="11087100" y="289801300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5440,7 +5440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="294525700"/>
+    <pos x="7391400" y="294525700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5460,7 +5460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="294525700"/>
+    <pos x="9239250" y="294525700"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -5480,7 +5480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="294525700"/>
+    <pos x="11087100" y="294525700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5500,7 +5500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="294525700"/>
+    <pos x="12934950" y="294525700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5520,7 +5520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="296373550"/>
+    <pos x="7391400" y="296373550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5540,7 +5540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="296373550"/>
+    <pos x="9239250" y="296373550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5560,7 +5560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="296373550"/>
+    <pos x="11087100" y="296373550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5580,7 +5580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="296373550"/>
+    <pos x="12934950" y="296373550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5600,7 +5600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="302336200"/>
+    <pos x="7391400" y="302336200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5620,7 +5620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="302336200"/>
+    <pos x="9239250" y="302336200"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -5640,7 +5640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="302336200"/>
+    <pos x="11087100" y="302336200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5660,7 +5660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="302336200"/>
+    <pos x="12934950" y="302336200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5680,7 +5680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="304184050"/>
+    <pos x="7391400" y="304184050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5700,7 +5700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="304184050"/>
+    <pos x="9239250" y="304184050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5720,7 +5720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="304184050"/>
+    <pos x="11087100" y="304184050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5740,7 +5740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="304184050"/>
+    <pos x="12934950" y="304184050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5760,7 +5760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="310553100"/>
+    <pos x="7391400" y="310553100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5780,7 +5780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="310553100"/>
+    <pos x="9239250" y="310553100"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5800,7 +5800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="310553100"/>
+    <pos x="11087100" y="310553100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5820,7 +5820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="310553100"/>
+    <pos x="12934950" y="310553100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5840,7 +5840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="312400950"/>
+    <pos x="7391400" y="312400950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5860,7 +5860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="312400950"/>
+    <pos x="9239250" y="312400950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5880,7 +5880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="312400950"/>
+    <pos x="11087100" y="312400950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5900,7 +5900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="312400950"/>
+    <pos x="12934950" y="312400950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5920,7 +5920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="314248800"/>
+    <pos x="7391400" y="314248800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5940,7 +5940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="314248800"/>
+    <pos x="9239250" y="314248800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5960,7 +5960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="314248800"/>
+    <pos x="11087100" y="314248800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5980,7 +5980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="314248800"/>
+    <pos x="12934950" y="314248800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6000,7 +6000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="316096650"/>
+    <pos x="7391400" y="316096650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6020,7 +6020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="321614800"/>
+    <pos x="7391400" y="321614800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6040,7 +6040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="321614800"/>
+    <pos x="9239250" y="321614800"/>
     <ext cx="1809750" cy="1466850"/>
     <pic>
       <nvPicPr>
@@ -6060,7 +6060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="321614800"/>
+    <pos x="11087100" y="321614800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6080,7 +6080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="321614800"/>
+    <pos x="12934950" y="321614800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6100,7 +6100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="323462650"/>
+    <pos x="7391400" y="323462650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6120,7 +6120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="323462650"/>
+    <pos x="9239250" y="323462650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6140,7 +6140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="323462650"/>
+    <pos x="11087100" y="323462650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6160,7 +6160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="323462650"/>
+    <pos x="12934950" y="323462650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6180,7 +6180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="325310500"/>
+    <pos x="7391400" y="325310500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6200,7 +6200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="325310500"/>
+    <pos x="9239250" y="325310500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6220,7 +6220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="332473300"/>
+    <pos x="7391400" y="332473300"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6240,7 +6240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="339064600"/>
+    <pos x="7391400" y="339064600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6260,7 +6260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="339064600"/>
+    <pos x="9239250" y="339064600"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -6280,7 +6280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="339064600"/>
+    <pos x="11087100" y="339064600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6300,7 +6300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="339064600"/>
+    <pos x="12934950" y="339064600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6320,7 +6320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="340912450"/>
+    <pos x="7391400" y="340912450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6340,7 +6340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="344233500"/>
+    <pos x="7391400" y="344233500"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6360,7 +6360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="351231200"/>
+    <pos x="7391400" y="351231200"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6380,7 +6380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="356831900"/>
+    <pos x="7391400" y="356831900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6400,7 +6400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="356831900"/>
+    <pos x="9239250" y="356831900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6420,7 +6420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="356831900"/>
+    <pos x="11087100" y="356831900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6440,7 +6440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="356831900"/>
+    <pos x="12934950" y="356831900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6460,7 +6460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="358679750"/>
+    <pos x="7391400" y="358679750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6480,7 +6480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="358679750"/>
+    <pos x="9239250" y="358679750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6500,7 +6500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="358679750"/>
+    <pos x="11087100" y="358679750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6520,7 +6520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="363626400"/>
+    <pos x="7391400" y="363626400"/>
     <ext cx="1190625" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6540,7 +6540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="369811300"/>
+    <pos x="7391400" y="369811300"/>
     <ext cx="1143000" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6560,7 +6560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="376834400"/>
+    <pos x="7391400" y="376834400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6580,7 +6580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="376834400"/>
+    <pos x="9239250" y="376834400"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -6600,7 +6600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="376834400"/>
+    <pos x="11087100" y="376834400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6620,7 +6620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="376834400"/>
+    <pos x="12934950" y="376834400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6640,7 +6640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="378682250"/>
+    <pos x="7391400" y="378682250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6660,7 +6660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="389724900"/>
+    <pos x="7391400" y="389724900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6680,7 +6680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="389724900"/>
+    <pos x="9239250" y="389724900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6700,7 +6700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="389724900"/>
+    <pos x="11087100" y="389724900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6720,7 +6720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="389724900"/>
+    <pos x="12934950" y="389724900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6740,7 +6740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="391572750"/>
+    <pos x="7391400" y="391572750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6760,7 +6760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="391572750"/>
+    <pos x="9239250" y="391572750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6780,7 +6780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="391572750"/>
+    <pos x="11087100" y="391572750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6800,7 +6800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="397535400"/>
+    <pos x="7391400" y="397535400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6820,7 +6820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="397535400"/>
+    <pos x="9239250" y="397535400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6840,7 +6840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="397535400"/>
+    <pos x="11087100" y="397535400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6860,7 +6860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="397535400"/>
+    <pos x="12934950" y="397535400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7178,7 +7178,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/10_세정(클렌징).xlsx
+++ b/카드_아키타입/10_세정(클렌징).xlsx
@@ -1508,7 +1508,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="74726800"/>
+    <pos x="7848600" y="74930000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1528,7 +1528,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="74726800"/>
+    <pos x="9696450" y="74930000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1548,7 +1548,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="74726800"/>
+    <pos x="11544300" y="74930000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1568,7 +1568,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="74726800"/>
+    <pos x="13392150" y="74930000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1588,7 +1588,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="76574650"/>
+    <pos x="7848600" y="76777850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1608,7 +1608,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="76574650"/>
+    <pos x="9696450" y="76777850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1628,7 +1628,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="76574650"/>
+    <pos x="11544300" y="76777850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1648,7 +1648,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="76574650"/>
+    <pos x="13392150" y="76777850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1668,7 +1668,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="78422499"/>
+    <pos x="7848600" y="78625700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1688,7 +1688,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="78422499"/>
+    <pos x="9696450" y="78625700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1708,7 +1708,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="83121500"/>
+    <pos x="7848600" y="83324700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1728,7 +1728,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="83121500"/>
+    <pos x="9696450" y="83324700"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -1748,7 +1748,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="83121500"/>
+    <pos x="11544300" y="83324700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1768,7 +1768,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="83121500"/>
+    <pos x="13392150" y="83324700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1788,7 +1788,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="84969350"/>
+    <pos x="7848600" y="85172550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1808,7 +1808,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="84969350"/>
+    <pos x="9696450" y="85172550"/>
     <ext cx="1809750" cy="1438275"/>
     <pic>
       <nvPicPr>
@@ -1828,7 +1828,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="91922600"/>
+    <pos x="7848600" y="92125800"/>
     <ext cx="1695450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1848,7 +1848,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="91922600"/>
+    <pos x="9696450" y="92125800"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1868,7 +1868,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="91922600"/>
+    <pos x="11544300" y="92125800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1888,7 +1888,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="91922600"/>
+    <pos x="13392150" y="92125800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1908,7 +1908,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="93770450"/>
+    <pos x="7848600" y="93973650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1928,7 +1928,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="93770450"/>
+    <pos x="9696450" y="93973650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1948,7 +1948,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="93770450"/>
+    <pos x="11544300" y="93973650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1968,7 +1968,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="93770450"/>
+    <pos x="13392150" y="93973650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1988,7 +1988,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="103974900"/>
+    <pos x="7848600" y="104178100"/>
     <ext cx="1200150" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2008,7 +2008,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="103974900"/>
+    <pos x="9696450" y="104178100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2028,7 +2028,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="103974900"/>
+    <pos x="11544300" y="104178100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2048,7 +2048,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="103974900"/>
+    <pos x="13392150" y="104178100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2068,7 +2068,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="105822750"/>
+    <pos x="7848600" y="106025950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2088,7 +2088,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="114401600"/>
+    <pos x="7848600" y="114604800"/>
     <ext cx="1295400" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2108,7 +2108,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="114401600"/>
+    <pos x="9696450" y="114604800"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2128,7 +2128,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="114401600"/>
+    <pos x="11544300" y="114604800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2148,7 +2148,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="114401600"/>
+    <pos x="13392150" y="114604800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2168,7 +2168,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="116249450"/>
+    <pos x="7848600" y="116452650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2188,7 +2188,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="116249450"/>
+    <pos x="9696450" y="116452650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2208,7 +2208,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="116249450"/>
+    <pos x="11544300" y="116452650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2228,7 +2228,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="116249450"/>
+    <pos x="13392150" y="116452650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2248,7 +2248,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="118097300"/>
+    <pos x="7848600" y="118300500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2268,7 +2268,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="118097300"/>
+    <pos x="9696450" y="118300500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2288,7 +2288,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="118097300"/>
+    <pos x="11544300" y="118300500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2308,7 +2308,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="126047500"/>
+    <pos x="7848600" y="126250700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2328,7 +2328,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="126047500"/>
+    <pos x="9696450" y="126250700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2348,7 +2348,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="126047500"/>
+    <pos x="11544300" y="126250700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2368,7 +2368,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="126047500"/>
+    <pos x="13392150" y="126250700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2388,7 +2388,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="127895350"/>
+    <pos x="7848600" y="128098550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2408,7 +2408,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="127895350"/>
+    <pos x="9696450" y="128098550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2428,7 +2428,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="127895350"/>
+    <pos x="11544300" y="128098550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2448,7 +2448,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="134442200"/>
+    <pos x="7848600" y="134645400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2468,7 +2468,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="134442200"/>
+    <pos x="9696450" y="134645400"/>
     <ext cx="1809750" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -2488,7 +2488,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="134442200"/>
+    <pos x="11544300" y="134645400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2508,7 +2508,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="134442200"/>
+    <pos x="13392150" y="134645400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2528,7 +2528,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="136290050"/>
+    <pos x="7848600" y="136493250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2548,7 +2548,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="136290050"/>
+    <pos x="9696450" y="136493250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2568,7 +2568,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="136290050"/>
+    <pos x="11544300" y="136493250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2588,7 +2588,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="141414500"/>
+    <pos x="7848600" y="141617700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2608,7 +2608,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="141414500"/>
+    <pos x="9696450" y="141617700"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2628,7 +2628,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="141414500"/>
+    <pos x="11544300" y="141617700"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2648,7 +2648,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="141414500"/>
+    <pos x="13392150" y="141617700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2668,7 +2668,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="143262350"/>
+    <pos x="7848600" y="143465550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2688,7 +2688,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="143262350"/>
+    <pos x="9696450" y="143465550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2708,7 +2708,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="143262350"/>
+    <pos x="11544300" y="143465550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2728,7 +2728,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="143262350"/>
+    <pos x="13392150" y="143465550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2748,7 +2748,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="145110200"/>
+    <pos x="7848600" y="145313400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2768,7 +2768,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="149402800"/>
+    <pos x="7848600" y="149606000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2788,7 +2788,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="149402800"/>
+    <pos x="9696450" y="149606000"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2808,7 +2808,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="149402800"/>
+    <pos x="11544300" y="149606000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2828,7 +2828,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="149402800"/>
+    <pos x="13392150" y="149606000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2848,7 +2848,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="151250650"/>
+    <pos x="7848600" y="151453850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2868,7 +2868,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="151250650"/>
+    <pos x="9696450" y="151453850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2888,7 +2888,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="151250650"/>
+    <pos x="11544300" y="151453850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2908,7 +2908,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="151250650"/>
+    <pos x="13392150" y="151453850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2928,7 +2928,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="156578300"/>
+    <pos x="7848600" y="156781500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2948,7 +2948,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="156578300"/>
+    <pos x="9696450" y="156781500"/>
     <ext cx="1809750" cy="1314450"/>
     <pic>
       <nvPicPr>
@@ -2968,7 +2968,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="156578300"/>
+    <pos x="11544300" y="156781500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2988,7 +2988,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="156578300"/>
+    <pos x="13392150" y="156781500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3008,7 +3008,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="158426150"/>
+    <pos x="7848600" y="158629350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3028,7 +3028,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="158426150"/>
+    <pos x="9696450" y="158629350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3048,7 +3048,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="158426150"/>
+    <pos x="11544300" y="158629350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3068,7 +3068,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="158426150"/>
+    <pos x="13392150" y="158629350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3088,7 +3088,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="164363400"/>
+    <pos x="7848600" y="164566600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3108,7 +3108,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="164363400"/>
+    <pos x="9696450" y="164566600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3128,7 +3128,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="164363400"/>
+    <pos x="11544300" y="164566600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3148,7 +3148,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="164363400"/>
+    <pos x="13392150" y="164566600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3168,7 +3168,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="166211250"/>
+    <pos x="7848600" y="166414450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3188,7 +3188,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="166211250"/>
+    <pos x="9696450" y="166414450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3208,7 +3208,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="166211250"/>
+    <pos x="11544300" y="166414450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3228,7 +3228,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="166211250"/>
+    <pos x="13392150" y="166414450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3248,7 +3248,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="168059100"/>
+    <pos x="7848600" y="168262300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3268,7 +3268,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="168059100"/>
+    <pos x="9696450" y="168262300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3288,7 +3288,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="168059100"/>
+    <pos x="11544300" y="168262300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3308,7 +3308,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="168059100"/>
+    <pos x="13392150" y="168262300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3328,7 +3328,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="169906950"/>
+    <pos x="7848600" y="170110150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3348,7 +3348,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="169906950"/>
+    <pos x="9696450" y="170110150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3368,7 +3368,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="177634900"/>
+    <pos x="7848600" y="177838100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3388,7 +3388,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="177634900"/>
+    <pos x="9696450" y="177838100"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3408,7 +3408,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="177634900"/>
+    <pos x="11544300" y="177838100"/>
     <ext cx="1809750" cy="1781175"/>
     <pic>
       <nvPicPr>
@@ -3428,7 +3428,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="177634900"/>
+    <pos x="13392150" y="177838100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3448,7 +3448,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="179482750"/>
+    <pos x="7848600" y="179685950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3468,7 +3468,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="179482750"/>
+    <pos x="9696450" y="179685950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3488,7 +3488,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="179482750"/>
+    <pos x="11544300" y="179685950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3508,7 +3508,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="179482750"/>
+    <pos x="13392150" y="179685950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3528,7 +3528,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="181330600"/>
+    <pos x="7848600" y="181533800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3548,7 +3548,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="186029600"/>
+    <pos x="7848600" y="186436000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3568,7 +3568,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="186029600"/>
+    <pos x="9696450" y="186436000"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3588,7 +3588,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="186029600"/>
+    <pos x="11544300" y="186436000"/>
     <ext cx="1809750" cy="676275"/>
     <pic>
       <nvPicPr>
@@ -3608,7 +3608,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="186029600"/>
+    <pos x="13392150" y="186436000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3628,7 +3628,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="187877450"/>
+    <pos x="7848600" y="188283850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3648,7 +3648,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="187877450"/>
+    <pos x="9696450" y="188283850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3668,7 +3668,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="187877450"/>
+    <pos x="11544300" y="188283850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3688,7 +3688,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="187877450"/>
+    <pos x="13392150" y="188283850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3708,7 +3708,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="189725300"/>
+    <pos x="7848600" y="190131700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3728,7 +3728,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="193611500"/>
+    <pos x="7848600" y="194017900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3748,7 +3748,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="193611500"/>
+    <pos x="9696450" y="194017900"/>
     <ext cx="1685925" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3768,7 +3768,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="193611500"/>
+    <pos x="11544300" y="194017900"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -3788,7 +3788,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="193611500"/>
+    <pos x="13392150" y="194017900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3808,7 +3808,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="195459350"/>
+    <pos x="7848600" y="195865750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3828,7 +3828,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="195459350"/>
+    <pos x="9696450" y="195865750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3848,7 +3848,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="195459350"/>
+    <pos x="11544300" y="195865750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3868,7 +3868,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="195459350"/>
+    <pos x="13392150" y="195865750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3888,7 +3888,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="197307200"/>
+    <pos x="7848600" y="197713600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3908,7 +3908,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="200380600"/>
+    <pos x="7848600" y="200787000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3928,7 +3928,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="200380600"/>
+    <pos x="9696450" y="200787000"/>
     <ext cx="1609725" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3948,7 +3948,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="200380600"/>
+    <pos x="11544300" y="200787000"/>
     <ext cx="1809750" cy="676275"/>
     <pic>
       <nvPicPr>
@@ -3968,7 +3968,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="200380600"/>
+    <pos x="13392150" y="200787000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3988,7 +3988,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="202228450"/>
+    <pos x="7848600" y="202634850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4008,7 +4008,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="202228450"/>
+    <pos x="9696450" y="202634850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4028,7 +4028,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="202228450"/>
+    <pos x="11544300" y="202634850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4048,7 +4048,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="202228450"/>
+    <pos x="13392150" y="202634850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4068,7 +4068,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="204076300"/>
+    <pos x="7848600" y="204482700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4088,7 +4088,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="207352900"/>
+    <pos x="7848600" y="207759300"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4108,7 +4108,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="207352900"/>
+    <pos x="9696450" y="207759300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4128,7 +4128,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="207352900"/>
+    <pos x="11544300" y="207759300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4148,7 +4148,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="207352900"/>
+    <pos x="13392150" y="207759300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4168,7 +4168,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="209200750"/>
+    <pos x="7848600" y="209607150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4188,7 +4188,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="209200750"/>
+    <pos x="9696450" y="209607150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4208,7 +4208,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="214731600"/>
+    <pos x="7848600" y="214934800"/>
     <ext cx="1314450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4228,7 +4228,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="214731600"/>
+    <pos x="9696450" y="214934800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4248,7 +4248,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="214731600"/>
+    <pos x="11544300" y="214934800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4268,7 +4268,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="214731600"/>
+    <pos x="13392150" y="214934800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4288,7 +4288,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="216579450"/>
+    <pos x="7848600" y="216782650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4308,7 +4308,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="216579450"/>
+    <pos x="9696450" y="216782650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4328,7 +4328,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="216579450"/>
+    <pos x="11544300" y="216782650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4348,7 +4348,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="216579450"/>
+    <pos x="13392150" y="216782650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4368,7 +4368,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="218427300"/>
+    <pos x="7848600" y="218630500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4388,7 +4388,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="229831900"/>
+    <pos x="7848600" y="230035100"/>
     <ext cx="1657350" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4408,7 +4408,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="229831900"/>
+    <pos x="9696450" y="230035100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4428,7 +4428,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="229831900"/>
+    <pos x="11544300" y="230035100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4448,7 +4448,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="229831900"/>
+    <pos x="13392150" y="230035100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4468,7 +4468,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="231679750"/>
+    <pos x="7848600" y="231882950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4488,7 +4488,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="231679750"/>
+    <pos x="9696450" y="231882950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4508,7 +4508,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="231679750"/>
+    <pos x="11544300" y="231882950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4528,7 +4528,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="238023400"/>
+    <pos x="7848600" y="238226600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4548,7 +4548,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="238023400"/>
+    <pos x="9696450" y="238226600"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -4568,7 +4568,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="238023400"/>
+    <pos x="11544300" y="238226600"/>
     <ext cx="1809750" cy="809625"/>
     <pic>
       <nvPicPr>
@@ -4588,7 +4588,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="238023400"/>
+    <pos x="13392150" y="238226600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4608,7 +4608,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="239871250"/>
+    <pos x="7848600" y="240074450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4628,7 +4628,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="239871250"/>
+    <pos x="9696450" y="240074450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4648,7 +4648,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="244182900"/>
+    <pos x="7848600" y="244386100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4668,7 +4668,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="244182900"/>
+    <pos x="9696450" y="244386100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4688,7 +4688,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="244182900"/>
+    <pos x="11544300" y="244386100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4708,7 +4708,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="244182900"/>
+    <pos x="13392150" y="244386100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4728,7 +4728,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="255422400"/>
+    <pos x="7848600" y="255625600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4748,7 +4748,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="255422400"/>
+    <pos x="9696450" y="255625600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4768,7 +4768,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="255422400"/>
+    <pos x="11544300" y="255625600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4788,7 +4788,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="255422400"/>
+    <pos x="13392150" y="255625600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4808,7 +4808,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="265849100"/>
+    <pos x="7848600" y="266052300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4828,7 +4828,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="265849100"/>
+    <pos x="9696450" y="266052300"/>
     <ext cx="1552575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4848,7 +4848,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="265849100"/>
+    <pos x="11544300" y="266052300"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -4868,7 +4868,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="265849100"/>
+    <pos x="13392150" y="266052300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4888,7 +4888,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="267696950"/>
+    <pos x="7848600" y="267900150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4908,7 +4908,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="267696950"/>
+    <pos x="9696450" y="267900150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4928,7 +4928,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="267696950"/>
+    <pos x="11544300" y="267900150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4948,7 +4948,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="267696950"/>
+    <pos x="13392150" y="267900150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4968,7 +4968,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="269544800"/>
+    <pos x="7848600" y="269748000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4988,7 +4988,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="269544800"/>
+    <pos x="9696450" y="269748000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5008,7 +5008,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="269544800"/>
+    <pos x="11544300" y="269748000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5028,7 +5028,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="269544800"/>
+    <pos x="13392150" y="269748000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5048,7 +5048,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="274447000"/>
+    <pos x="7848600" y="274650200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5068,7 +5068,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="274447000"/>
+    <pos x="9696450" y="274650200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5088,7 +5088,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="274447000"/>
+    <pos x="11544300" y="274650200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5108,7 +5108,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="274447000"/>
+    <pos x="13392150" y="274650200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7482,10 +7482,10 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>세틸알코올+지방산 유도체를 반응시켜 만든 에스테르오일, / 끈적임이 없고 가볍고 산뜻한 사용감</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="n"/>
+          <t>세틸알코올+지방산 유도체를 반응시켜 만든 에스테르오일 · 끈적임이 없고 가볍고 산뜻한 사용감</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
@@ -7510,10 +7510,10 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>층분리 현상 방지, / 물에 잘 씻길 수 있도록 도와줌</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="n"/>
+          <t>층분리 현상 방지 · 물에 잘 씻길 수 있도록 도와줌</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>20모유에 들어있는 / 라우릭산 풍부, / 달콤한 향</t>
+          <t>20모유에 들어있는 · 라우릭산 풍부 · 달콤한 향</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -7719,10 +7719,10 @@
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>층분리 현상 방지, / 물에 잘 씻길 수 있도록 도와줌</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="n"/>
+          <t>층분리 현상 방지 · 물에 잘 씻길 수 있도록 도와줌</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr"/>
     </row>
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>포도씨오일, / 해바라기오일, 아몬드오일 등 / 가벼운 오일</t>
+          <t>포도씨오일 · 해바라기오일, 아몬드오일 등 · 가벼운 오일</t>
         </is>
       </c>
     </row>
@@ -7908,10 +7908,10 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>세틸알코올+지방산 유도체를 반응시켜 / 만든 에스테르오일, / 끈적임이 없고 가볍고 산뜻한 사용감</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="n"/>
+          <t>세틸알코올+지방산 유도체를 반응시켜 · 만든 에스테르오일 · 끈적임이 없고 가볍고 산뜻한 사용감</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>천연 순한 세정성분(유기농 라우릴/데실 글루코이드, PCG)으로 구성.풍성하고 탄력있는 거품, 사용 후 촉촉함, 약산성</t>
+          <t>천연 순한 세정성분(유기농 라우릴 · 데실 글루코이드, PCG)으로 구성.풍성하고 탄력있는 거품, 사용 후 촉촉함, 약산성</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>수입화장품 S사 / 피테라에센스의 주요 성분. / 탄력발효</t>
+          <t>수입화장품 S사 · 피테라에센스의 주요 성분. · 탄력발효</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>300g 맞춤, / (네롤리 등) 아로마 오일, / 가용화제 그리고 보존제 처방.</t>
+          <t>300g 맞춤 · (네롤리 등) 아로마 오일 · 가용화제 그리고 보존제 처방.</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
@@ -8662,10 +8662,10 @@
       </c>
       <c r="E67" s="20" t="inlineStr">
         <is>
-          <t>바닷물 등에 존재하며 / 균형을 유지해주는 약알카리성분, 탈취, 중화,발포, / 연마, 연수</t>
-        </is>
-      </c>
-      <c r="F67" s="20" t="n"/>
+          <t>바닷물 등에 존재하며 · 균형을 유지해주는 약알카리성분, 탈취, 중화,발포 · 연마, 연수</t>
+        </is>
+      </c>
+      <c r="F67" s="20" t="inlineStr"/>
     </row>
     <row r="68" ht="96" customHeight="1">
       <c r="A68" s="20" t="inlineStr">
@@ -8690,10 +8690,10 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>자작나무와 같은 / 활엽수에서 추출. / 설탕과 대등한 단맛을 내지만 충치균의 먹이가 되지 않고 입안의 산도를 떨어뜨리지 않는 충치예방에 효과가 있는 새로운 감미료</t>
-        </is>
-      </c>
-      <c r="F68" s="20" t="n"/>
+          <t>자작나무와 같은 · 활엽수에서 추출. · 설탕과 대등한 단맛을 내지만 충치균의 먹이가 되지 않고 입안의 산도를 떨어뜨리지 않는 충치예방에 효과가 있는 새로운 감미료</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="inlineStr"/>
     </row>
     <row r="69" ht="48" customHeight="1">
       <c r="A69" s="20" t="inlineStr">
@@ -8750,10 +8750,10 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>사탕수수에서 채취. 점증제 / ※양을 정확하게 계량하지 않으면 너무 뻑뻑하게 / 됩니다.</t>
-        </is>
-      </c>
-      <c r="F70" s="20" t="n"/>
+          <t>사탕수수에서 채취. 점증제 · ※양을 정확하게 계량하지 않으면 너무 뻑뻑하게 · 됩니다.</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr"/>
     </row>
     <row r="71" ht="64" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>사과주스로 만든 물비누, / 밀도가 높고 풍성한 기포형성, 단백질 변성이 없음, / 양치 후 음식맛을 그대로</t>
+          <t>사과주스로 만든 물비누 · 밀도가 높고 풍성한 기포형성, 단백질 변성이 없음 · 양치 후 음식맛을 그대로</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>유용미생물을 발효해 / 활성화시킨 액, / 잇몸건강, 구취예방</t>
+          <t>유용미생물을 발효해 · 활성화시킨 액 · 잇몸건강, 구취예방</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>5차 필터링, / UV살균처리 정제수</t>
+          <t>5차 필터링 · UV살균처리 정제수</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>티트리(항균), / 스피아민트 등</t>
+          <t>티트리(항균) · 스피아민트 등</t>
         </is>
       </c>
     </row>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>사과주스에서 얻은 계면활성제, / 피부단백질 변성없고 생분해가 잘됨</t>
+          <t>사과주스에서 얻은 계면활성제 · 피부단백질 변성없고 생분해가 잘됨</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>브로콜리, / 파프리카추출물</t>
+          <t>브로콜리 · 파프리카추출물</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
           <t>피부 보호막, 촉촉함이 오래유지</t>
         </is>
       </c>
-      <c r="F87" s="10" t="n"/>
+      <c r="F87" s="10" t="inlineStr"/>
     </row>
     <row r="88" ht="32" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>오렌지,라벤더, / 캐모마일로먼</t>
+          <t>오렌지,라벤더 · 캐모마일로먼</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="32" customHeight="1">
+    <row r="100" ht="48" customHeight="1">
       <c r="A100" s="20" t="inlineStr">
         <is>
           <t>버가못에센셜오일</t>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="F100" s="20" t="inlineStr">
         <is>
-          <t>라벤더, 티트리, 로먼/저먼캐모마일</t>
+          <t>라벤더, 티트리, 로먼 · 저먼캐모마일</t>
         </is>
       </c>
     </row>
@@ -9621,10 +9621,10 @@
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>천연 순한 세정성분(애플계면활성제, 데실/라우릴 글루코이드) 으로 구성. 풍성한 거품, / 사용 후 촉촉함, 약산성</t>
-        </is>
-      </c>
-      <c r="F110" s="10" t="n"/>
+          <t>천연 순한 세정성분(애플계면활성제, 데실 · 라우릴 글루코이드) 으로 구성. 풍성한 거품 · 사용 후 촉촉함, 약산성</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr"/>
     </row>
     <row r="111" ht="32" customHeight="1">
       <c r="A111" s="10" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>장미꽃수. 민감 피부, 진정,</t>
+          <t>장미꽃수. 민감 피부, 진정</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>피부 타입에 따른 / 워터나 추출물</t>
+          <t>피부 타입에 따른 · 워터나 추출물</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>300g 맞춤 아로마 오일, / 가용화제 그리고 보존제 처방</t>
+          <t>300g 맞춤 아로마 오일 · 가용화제 그리고 보존제 처방</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E121" s="20" t="inlineStr">
         <is>
-          <t>피지 성분 비슷, / 가볍고 피부유연</t>
+          <t>피지 성분 비슷 · 가볍고 피부유연</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
         <is>
-          <t>골든호호바, / 아르간오일 등</t>
+          <t>골든호호바 · 아르간오일 등</t>
         </is>
       </c>
     </row>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F123" s="20" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="E125" s="20" t="inlineStr">
         <is>
-          <t>올리브오일 유래, / 클렌징오일이 물에 씻기도록 함.</t>
+          <t>올리브오일 유래 · 클렌징오일이 물에 씻기도록 함.</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
@@ -10153,10 +10153,10 @@
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>천연 순한 세정성분(애플계면활성제, 데실/라우릴 글루코이드) 으로 구성. 풍성한 거품, / 사용 후 촉촉함, 약산성</t>
-        </is>
-      </c>
-      <c r="F135" s="10" t="n"/>
+          <t>천연 순한 세정성분(애플계면활성제, 데실 · 라우릴 글루코이드) 으로 구성. 풍성한 거품 · 사용 후 촉촉함, 약산성</t>
+        </is>
+      </c>
+      <c r="F135" s="10" t="inlineStr"/>
     </row>
     <row r="136" ht="48" customHeight="1">
       <c r="A136" s="10" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>피부 타입에 따른 / 추출물</t>
+          <t>피부 타입에 따른 · 추출물</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워, 러블리레몬, / 그린프레쉬 아로마수</t>
+          <t>로즈플라워, 러블리레몬 · 그린프레쉬 아로마수</t>
         </is>
       </c>
     </row>
@@ -10386,10 +10386,10 @@
       </c>
       <c r="E147" s="20" t="inlineStr">
         <is>
-          <t>천연 순한 세정성분(애플계면활성제, 데실/라우릴 글루코이드), 피부 진정성분 알란토인 함유으로 구성. 풍성한 거품, 촉촉함, 약산성</t>
-        </is>
-      </c>
-      <c r="F147" s="20" t="n"/>
+          <t>천연 순한 세정성분(애플계면활성제, 데실 · 라우릴 글루코이드), 피부 진정성분 알란토인 함유으로 구성. 풍성한 거품, 촉촉함, 약산성</t>
+        </is>
+      </c>
+      <c r="F147" s="20" t="inlineStr"/>
     </row>
     <row r="148" ht="48" customHeight="1">
       <c r="A148" s="20" t="inlineStr">
@@ -10414,10 +10414,10 @@
       </c>
       <c r="E148" s="20" t="inlineStr">
         <is>
-          <t>유기농 갈근, 쐐기품, 파파야잎,겐티아나 / ,비누풀뿌리 추출물 천연 거품, 각질제거</t>
-        </is>
-      </c>
-      <c r="F148" s="20" t="n"/>
+          <t>유기농 갈근, 쐐기품, 파파야잎,겐티아나 · 비누풀뿌리 추출물 천연 거품, 각질제거</t>
+        </is>
+      </c>
+      <c r="F148" s="20" t="inlineStr"/>
     </row>
     <row r="149" ht="32" customHeight="1">
       <c r="A149" s="20" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="F149" s="20" t="inlineStr">
         <is>
-          <t>녹차, / 어성초추출물</t>
+          <t>녹차 · 어성초추출물</t>
         </is>
       </c>
     </row>
@@ -10474,12 +10474,12 @@
       </c>
       <c r="E150" s="20" t="inlineStr">
         <is>
-          <t>300g 맞춤. / 편백, 페퍼민트, 패출리 에센셜오일, / 가용화제 그리고 보존제 처방.</t>
+          <t>300g 맞춤. · 편백, 페퍼민트, 패출리 에센셜오일 · 가용화제 그리고 보존제 처방.</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
         <is>
-          <t>피부타입에 / 맞는 아로마수 선택 / 러블리 로즈, 오렌지 플라워 등</t>
+          <t>피부타입에 · 맞는 아로마수 선택 · 러블리 로즈, 오렌지 플라워 등</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="E160" s="10" t="inlineStr">
         <is>
-          <t>고농축 카렌듈라꽃 추출물 함유, / 올레인산과 비타민A성분 풍부</t>
+          <t>고농축 카렌듈라꽃 추출물 함유 · 올레인산과 비타민A성분 풍부</t>
         </is>
       </c>
       <c r="F160" s="10" t="inlineStr">
@@ -10682,10 +10682,10 @@
       </c>
       <c r="E161" s="10" t="inlineStr">
         <is>
-          <t>층분리 현상 방지, / 물에 잘 씻길 수 있도록 도와줌</t>
-        </is>
-      </c>
-      <c r="F161" s="10" t="n"/>
+          <t>층분리 현상 방지 · 물에 잘 씻길 수 있도록 도와줌</t>
+        </is>
+      </c>
+      <c r="F161" s="10" t="inlineStr"/>
     </row>
     <row r="162" ht="32" customHeight="1">
       <c r="A162" s="10" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="E172" s="20" t="inlineStr">
         <is>
-          <t>천연 순한 세정성분(유기농 라우릴/데실 글루코이드, PCG)으로 구성.풍성하고 탄력있는 거품, 사용 후 촉촉함, 약산성</t>
+          <t>천연 순한 세정성분(유기농 라우릴 · 데실 글루코이드, PCG)으로 구성.풍성하고 탄력있는 거품, 사용 후 촉촉함, 약산성</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="E173" s="20" t="inlineStr">
         <is>
-          <t>장미 수증기추출법으로 추출, / 장미의 수용성 성분 / 다량 함유</t>
+          <t>장미 수증기추출법으로 추출 · 장미의 수용성 성분 · 다량 함유</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="F174" s="20" t="inlineStr">
         <is>
-          <t>콜라겐, / 마린콜라겐</t>
+          <t>콜라겐 · 마린콜라겐</t>
         </is>
       </c>
     </row>
@@ -10982,12 +10982,12 @@
       </c>
       <c r="E175" s="20" t="inlineStr">
         <is>
-          <t>300g 맞춤. / (로즈제라늄 등) 아로마 오일, / 가용화제 그리고 보존제 처방.</t>
+          <t>300g 맞춤. · (로즈제라늄 등) 아로마 오일 · 가용화제 그리고 보존제 처방.</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
         <is>
-          <t>원하는 / 아로마수</t>
+          <t>원하는 · 아로마수</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="E184" s="10" t="inlineStr">
         <is>
-          <t>천연 순한 세정성분 / (유기농 라우릴/데실 글루코이드, PCG) 으로 구성. / 풍성한 거품, / 사용 후 촉촉함, 약산성</t>
+          <t>천연 순한 세정성분 · (유기농 라우릴 · 데실 글루코이드, PCG) 으로 구성. · 풍성한 거품 · 사용 후 촉촉함, 약산성</t>
         </is>
       </c>
       <c r="F184" s="10" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="F185" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 추출물</t>
+          <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="E187" s="10" t="inlineStr">
         <is>
-          <t>300g 맞춤. 아로마 오일, / 가용화제 그리고 보존제 처방.</t>
+          <t>300g 맞춤. 아로마 오일 · 가용화제 그리고 보존제 처방.</t>
         </is>
       </c>
       <c r="F187" s="10" t="inlineStr">
@@ -11380,10 +11380,10 @@
       </c>
       <c r="E196" s="20" t="inlineStr">
         <is>
-          <t>애플계면활성제, 라우릴글루코사이드, / 코코베타인, 글루카메이트, 알로에베라잎즙, 편백수 등 에코인증, 식물유래 순한 원료 함유.</t>
-        </is>
-      </c>
-      <c r="F196" s="20" t="n"/>
+          <t>애플계면활성제, 라우릴글루코사이드 · 코코베타인, 글루카메이트, 알로에베라잎즙, 편백수 등 에코인증, 식물유래 순한 원료 함유.</t>
+        </is>
+      </c>
+      <c r="F196" s="20" t="inlineStr"/>
     </row>
     <row r="197" ht="16" customHeight="1">
       <c r="A197" s="20" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="E198" s="20" t="inlineStr">
         <is>
-          <t>레몬EO, 레몬글라스EO, / 로즈우드EO을 블랜딩</t>
+          <t>레몬EO, 레몬글라스EO · 로즈우드EO을 블랜딩</t>
         </is>
       </c>
       <c r="F198" s="20" t="inlineStr">
@@ -11604,7 +11604,7 @@
           <t>애플계면활성제, 라우릴글루코사이드 알로에베라잎즙, 편백수 등 에코인증, 식물유래 순한 원료 함유.</t>
         </is>
       </c>
-      <c r="F207" s="10" t="n"/>
+      <c r="F207" s="10" t="inlineStr"/>
     </row>
     <row r="208" ht="48" customHeight="1">
       <c r="A208" s="10" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E209" s="10" t="inlineStr">
         <is>
-          <t>금잔화추출물, / 민감 트러블완화.</t>
+          <t>금잔화추출물 · 민감 트러블완화.</t>
         </is>
       </c>
       <c r="F209" s="10" t="inlineStr">
         <is>
-          <t>알란토인, / 감초추출물</t>
+          <t>알란토인 · 감초추출물</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F220" s="20" t="inlineStr">
         <is>
-          <t>원하는 / 추출물</t>
+          <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F221" s="20" t="inlineStr">
         <is>
-          <t>티트리(항균), / 스피아민트 등</t>
+          <t>티트리(항균) · 스피아민트 등</t>
         </is>
       </c>
     </row>
@@ -12145,10 +12145,10 @@
       </c>
       <c r="E233" s="10" t="inlineStr">
         <is>
-          <t>미국산, 식품등급, 아주 미세분말, / 치아 화이트</t>
-        </is>
-      </c>
-      <c r="F233" s="10" t="n"/>
+          <t>미국산, 식품등급, 아주 미세분말 · 치아 화이트</t>
+        </is>
+      </c>
+      <c r="F233" s="10" t="inlineStr"/>
     </row>
     <row r="234" ht="48" customHeight="1">
       <c r="A234" s="10" t="inlineStr">
@@ -12176,7 +12176,7 @@
           <t>설탕과 대등한 단맛을 내지만 충치균의 먹이가 되지 않음. 충치예방 감미료.</t>
         </is>
       </c>
-      <c r="F234" s="10" t="n"/>
+      <c r="F234" s="10" t="inlineStr"/>
     </row>
     <row r="235" ht="48" customHeight="1">
       <c r="A235" s="10" t="inlineStr">
@@ -12236,7 +12236,7 @@
           <t>점도 조절</t>
         </is>
       </c>
-      <c r="F236" s="10" t="n"/>
+      <c r="F236" s="10" t="inlineStr"/>
     </row>
     <row r="237" ht="64" customHeight="1">
       <c r="A237" s="10" t="inlineStr">
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E237" s="10" t="inlineStr">
         <is>
-          <t>순수한 물 , / 완성품의 색을 고르게.</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F237" s="10" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="E239" s="10" t="inlineStr">
         <is>
-          <t>세정, / 사과주스로 만든 거품제,</t>
+          <t>세정 · 사과주스로 만든 거품제</t>
         </is>
       </c>
       <c r="F239" s="10" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="F240" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -12389,7 +12389,7 @@
       </c>
       <c r="E241" s="10" t="inlineStr">
         <is>
-          <t>천연박하오일, / 입안을 상쾌하게</t>
+          <t>천연박하오일 · 입안을 상쾌하게</t>
         </is>
       </c>
       <c r="F241" s="10" t="inlineStr">
@@ -12551,7 +12551,7 @@
         </is>
       </c>
     </row>
-    <row r="251" ht="64" customHeight="1">
+    <row r="251" ht="80" customHeight="1">
       <c r="A251" s="20" t="inlineStr">
         <is>
           <t>시카 판테놀 / 폼클렌징베이스</t>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="E251" s="20" t="inlineStr">
         <is>
-          <t>천연 순한 세정성분 / (유기농 라우릴/데실 글루코이드, PCG)으로 구성. / 풍성하고 탄력있는 거품, 사용 후 촉촉함, 약산성</t>
+          <t>천연 순한 세정성분 · (유기농 라우릴 · 데실 글루코이드, PCG)으로 구성. · 풍성하고 탄력있는 거품, 사용 후 촉촉함, 약산성</t>
         </is>
       </c>
       <c r="F251" s="20" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="E252" s="20" t="inlineStr">
         <is>
-          <t>폴리페놀 풍부, / 항산화</t>
+          <t>폴리페놀 풍부 · 항산화</t>
         </is>
       </c>
       <c r="F252" s="20" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="F253" s="20" t="inlineStr">
         <is>
-          <t>어성초 / , 카렌듈라추출물 등</t>
+          <t>어성초 · 카렌듈라추출물 등</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="F254" s="20" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -12830,10 +12830,10 @@
       </c>
       <c r="E263" s="10" t="inlineStr">
         <is>
-          <t>애플계면활성제, / 라우릴글루코사이드, / 코코베타인, 글루카메이트, / 알로에베라잎즙, 편백수 등 에코인증, / 식물유래 순한 원료 함유.</t>
-        </is>
-      </c>
-      <c r="F263" s="10" t="n"/>
+          <t>애플계면활성제 · 라우릴글루코사이드 · 코코베타인, 글루카메이트 · 알로에베라잎즙, 편백수 등 에코인증 · 식물유래 순한 원료 함유.</t>
+        </is>
+      </c>
+      <c r="F263" s="10" t="inlineStr"/>
     </row>
     <row r="264" ht="64" customHeight="1">
       <c r="A264" s="10" t="inlineStr">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="F264" s="10" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="E267" s="10" t="inlineStr">
         <is>
-          <t>레몬, 레몬글라스, / 로즈우드EO 3가지 복합오일</t>
+          <t>레몬, 레몬글라스 · 로즈우드EO 3가지 복합오일</t>
         </is>
       </c>
       <c r="F267" s="10" t="inlineStr">
@@ -13095,10 +13095,10 @@
       </c>
       <c r="E276" s="20" t="inlineStr">
         <is>
-          <t>식물유래 순한 원료 함유. / 애플계면활성제, / 라우릴글루코사이드, / 코코베타인, 글루카메이트, / 알로에베라잎즙, 편백수 등 / 에코인증</t>
-        </is>
-      </c>
-      <c r="F276" s="20" t="n"/>
+          <t>식물유래 순한 원료 함유. · 애플계면활성제 · 라우릴글루코사이드 · 코코베타인, 글루카메이트 · 알로에베라잎즙, 편백수 등 · 에코인증</t>
+        </is>
+      </c>
+      <c r="F276" s="20" t="inlineStr"/>
     </row>
     <row r="277" ht="16" customHeight="1">
       <c r="A277" s="20" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F277" s="20" t="inlineStr">
         <is>
-          <t>원하는 / 추출물</t>
+          <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
@@ -13155,12 +13155,12 @@
       </c>
       <c r="E278" s="20" t="inlineStr">
         <is>
-          <t>자몽껍질에서 추출, / 배출, 슬림</t>
+          <t>자몽껍질에서 추출 · 배출, 슬림</t>
         </is>
       </c>
       <c r="F278" s="20" t="inlineStr">
         <is>
-          <t>슬림에 도움을 주는 에센셜오일 싸이프러스, / 제라늄, / 펜넬EO</t>
+          <t>슬림에 도움을 주는 에센셜오일 싸이프러스 · 제라늄 · 펜넬EO</t>
         </is>
       </c>
     </row>
@@ -13308,10 +13308,10 @@
       </c>
       <c r="E287" s="10" t="inlineStr">
         <is>
-          <t>애플계면활성제, / 라우릴글루코사이드, / 코코베타인, 글루카메이트, / 알로에베라잎즙, 편백수 등 에코인증, / 식물유래 순한 원료 함유.</t>
-        </is>
-      </c>
-      <c r="F287" s="10" t="n"/>
+          <t>애플계면활성제 · 라우릴글루코사이드 · 코코베타인, 글루카메이트 · 알로에베라잎즙, 편백수 등 에코인증 · 식물유래 순한 원료 함유.</t>
+        </is>
+      </c>
+      <c r="F287" s="10" t="inlineStr"/>
     </row>
     <row r="288" ht="64" customHeight="1">
       <c r="A288" s="10" t="inlineStr">
@@ -13368,12 +13368,12 @@
       </c>
       <c r="E289" s="10" t="inlineStr">
         <is>
-          <t>피부 보호막, / 촉촉함이 오래</t>
+          <t>피부 보호막 · 촉촉함이 오래</t>
         </is>
       </c>
       <c r="F289" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 추출물</t>
+          <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
@@ -13542,10 +13542,10 @@
       </c>
       <c r="E299" s="20" t="inlineStr">
         <is>
-          <t>천연 순한 세정성분(애플계면활성제, / 데실/라우릴 글루코이드) 으로 구성. / 풍성한 거품, 사용 후 촉촉함, 약산성</t>
-        </is>
-      </c>
-      <c r="F299" s="20" t="n"/>
+          <t>천연 순한 세정성분(애플계면활성제 · 데실 · 라우릴 글루코이드) 으로 구성. · 풍성한 거품, 사용 후 촉촉함, 약산성</t>
+        </is>
+      </c>
+      <c r="F299" s="20" t="inlineStr"/>
     </row>
     <row r="300" ht="32" customHeight="1">
       <c r="A300" s="20" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="E300" s="20" t="inlineStr">
         <is>
-          <t>병풀의 핵심 성분, 진정. / 트러블 개선, 피부 장벽 강화</t>
+          <t>병풀의 핵심 성분, 진정. · 트러블 개선, 피부 장벽 강화</t>
         </is>
       </c>
       <c r="F300" s="20" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="E301" s="20" t="inlineStr">
         <is>
-          <t>모공 세정 / 해독효소 활성화, 항산화</t>
-        </is>
-      </c>
-      <c r="F301" s="20" t="n"/>
-    </row>
-    <row r="302" ht="48" customHeight="1">
+          <t>모공 세정 · 해독효소 활성화, 항산화</t>
+        </is>
+      </c>
+      <c r="F301" s="20" t="inlineStr"/>
+    </row>
+    <row r="302" ht="32" customHeight="1">
       <c r="A302" s="20" t="inlineStr">
         <is>
           <t>라임캔디 / 블렌딩오일</t>
@@ -13630,12 +13630,12 @@
       </c>
       <c r="E302" s="20" t="inlineStr">
         <is>
-          <t>라임EO, 스윗오렌지EO, 레몬EO, / 로즈마리EO를 블렌딩한 오일.</t>
+          <t>라임EO, 스윗오렌지EO, 레몬EO · 로즈마리EO를 블렌딩한 오일.</t>
         </is>
       </c>
       <c r="F302" s="20" t="inlineStr">
         <is>
-          <t>레몬쥬스 / 블렌딩오일</t>
+          <t>레몬쥬스 · 블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -13784,7 +13784,7 @@
           <t>연마 작용</t>
         </is>
       </c>
-      <c r="F311" s="10" t="n"/>
+      <c r="F311" s="10" t="inlineStr"/>
     </row>
     <row r="312" ht="16" customHeight="1">
       <c r="A312" s="10" t="inlineStr">
@@ -13808,7 +13808,7 @@
           <t>연마 작용</t>
         </is>
       </c>
-      <c r="F312" s="10" t="n"/>
+      <c r="F312" s="10" t="inlineStr"/>
     </row>
     <row r="313" ht="96" customHeight="1">
       <c r="A313" s="10" t="inlineStr">
@@ -13829,10 +13829,10 @@
       </c>
       <c r="E313" s="10" t="inlineStr">
         <is>
-          <t>자작나무와 같은 / 활엽수에서 추출. / 설탕과 대등한 단맛을 내지만 충치균의 먹이가 되지 않고 입안의 산도를 떨어뜨리지 않는 충치예방에 효과가 있는 새로운 감미료</t>
-        </is>
-      </c>
-      <c r="F313" s="10" t="n"/>
+          <t>자작나무와 같은 · 활엽수에서 추출. · 설탕과 대등한 단맛을 내지만 충치균의 먹이가 되지 않고 입안의 산도를 떨어뜨리지 않는 충치예방에 효과가 있는 새로운 감미료</t>
+        </is>
+      </c>
+      <c r="F313" s="10" t="inlineStr"/>
     </row>
     <row r="314" ht="64" customHeight="1">
       <c r="A314" s="10" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="E314" s="10" t="inlineStr">
         <is>
-          <t>순수한 물 , / 완성품의 색을 고르게.</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F314" s="10" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -13881,12 +13881,12 @@
       </c>
       <c r="E315" s="10" t="inlineStr">
         <is>
-          <t>정밀 저울을 이용하세요. 컴프리뿌리, / 100%알란토인, 진정, 트러블피부관리 / 분말의 경우 0.3%가 넘으면 다 녹지 않고 침전됩니다. / 뿌옇게..^^</t>
+          <t>정밀 저울을 이용하세요. 컴프리뿌리 · 100%알란토인, 진정, 트러블피부관리 · 분말의 경우 0.3%가 넘으면 다 녹지 않고 침전됩니다. · 뿌옇게..^^</t>
         </is>
       </c>
       <c r="F315" s="10" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -13914,7 +13914,7 @@
       </c>
       <c r="F316" s="10" t="inlineStr">
         <is>
-          <t>유기농 카밍 5솔루션, / 캐모마일, 카렌듈라 등.</t>
+          <t>유기농 카밍 5솔루션 · 캐모마일, 카렌듈라 등.</t>
         </is>
       </c>
     </row>
@@ -13965,12 +13965,12 @@
       </c>
       <c r="E318" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 / 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
+          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 · 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
         </is>
       </c>
       <c r="F318" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -13993,7 +13993,7 @@
       </c>
       <c r="E319" s="10" t="inlineStr">
         <is>
-          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
+          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
       <c r="F319" s="10" t="inlineStr">
@@ -14021,10 +14021,10 @@
       </c>
       <c r="E320" s="10" t="inlineStr">
         <is>
-          <t>사탕수수에서 채취. 점증제 / ※양을 정확하게 계량하지 않으면 너무 뻑뻑하게 / 됩니다.</t>
-        </is>
-      </c>
-      <c r="F320" s="10" t="n"/>
+          <t>사탕수수에서 채취. 점증제 · ※양을 정확하게 계량하지 않으면 너무 뻑뻑하게 · 됩니다.</t>
+        </is>
+      </c>
+      <c r="F320" s="10" t="inlineStr"/>
     </row>
     <row r="321" ht="48" customHeight="1">
       <c r="A321" s="10" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="F321" s="10" t="inlineStr">
         <is>
-          <t>아로마테라피효과 / 원하는 에센셜오일</t>
+          <t>아로마테라피효과 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="F331" s="20" t="inlineStr">
         <is>
-          <t>포도씨오일, / 해바라기오일, 아몬드오일 등 / 가벼운 오일</t>
+          <t>포도씨오일 · 해바라기오일, 아몬드오일 등 · 가벼운 오일</t>
         </is>
       </c>
     </row>
@@ -14265,10 +14265,10 @@
       </c>
       <c r="E332" s="20" t="inlineStr">
         <is>
-          <t>오일, 피지,노폐물이 / 물에 씻기게하는 역할, / 층분리현상없음</t>
-        </is>
-      </c>
-      <c r="F332" s="20" t="n"/>
+          <t>오일, 피지,노폐물이 · 물에 씻기게하는 역할 · 층분리현상없음</t>
+        </is>
+      </c>
+      <c r="F332" s="20" t="inlineStr"/>
     </row>
     <row r="333" ht="64" customHeight="1">
       <c r="A333" s="20" t="inlineStr">
@@ -14293,12 +14293,12 @@
       </c>
       <c r="E333" s="20" t="inlineStr">
         <is>
-          <t>티트리, 라벤더, / 버가못FCF, 레몬FCF에센셜오일 / 블렌딩</t>
+          <t>티트리, 라벤더 · 버가못FCF, 레몬FCF에센셜오일 · 블렌딩</t>
         </is>
       </c>
       <c r="F333" s="20" t="inlineStr">
         <is>
-          <t>레몬 또는 / 레몬쥬스 / 블렌딩오일</t>
+          <t>레몬 또는 · 레몬쥬스 · 블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="E342" s="10" t="inlineStr">
         <is>
-          <t>피지성분과 비슷, / 빠른흡수</t>
+          <t>피지성분과 비슷 · 빠른흡수</t>
         </is>
       </c>
       <c r="F342" s="10" t="inlineStr">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="F343" s="10" t="inlineStr">
         <is>
-          <t>포도씨오일, / 해바라기오일, 아몬드오일 등 / 가벼운 오일</t>
+          <t>포도씨오일 · 해바라기오일, 아몬드오일 등 · 가벼운 오일</t>
         </is>
       </c>
     </row>
@@ -14512,10 +14512,10 @@
       </c>
       <c r="E344" s="10" t="inlineStr">
         <is>
-          <t>층분리 현상 방지, / 물에 잘 씻길 수 있도록 도와줌 .</t>
-        </is>
-      </c>
-      <c r="F344" s="10" t="n"/>
+          <t>층분리 현상 방지 · 물에 잘 씻길 수 있도록 도와줌 .</t>
+        </is>
+      </c>
+      <c r="F344" s="10" t="inlineStr"/>
     </row>
     <row r="345" ht="32" customHeight="1">
       <c r="A345" s="10" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="E345" s="10" t="inlineStr">
         <is>
-          <t>레몬, 레몬글라스, 로즈우드 / 에센셜오일 블렌딩</t>
+          <t>레몬, 레몬글라스, 로즈우드 · 에센셜오일 블렌딩</t>
         </is>
       </c>
       <c r="F345" s="10" t="inlineStr">
@@ -14679,12 +14679,12 @@
       </c>
       <c r="E354" s="20" t="inlineStr">
         <is>
-          <t>사탕무(보습)에서 추출한 당+코코넛오일 로 / 만든 양쪽성 계면활성제</t>
+          <t>사탕무(보습)에서 추출한 당+코코넛오일 로 · 만든 양쪽성 계면활성제</t>
         </is>
       </c>
       <c r="F354" s="20" t="inlineStr">
         <is>
-          <t>애플 / 계면활성제</t>
+          <t>애플 · 계면활성제</t>
         </is>
       </c>
     </row>
@@ -14711,10 +14711,10 @@
       </c>
       <c r="E355" s="20" t="inlineStr">
         <is>
-          <t>아미노산 계열 음이온, (글리신) 보습, / 생분해, 저자극</t>
-        </is>
-      </c>
-      <c r="F355" s="20" t="n"/>
+          <t>아미노산 계열 음이온, (글리신) 보습 · 생분해, 저자극</t>
+        </is>
+      </c>
+      <c r="F355" s="20" t="inlineStr"/>
     </row>
     <row r="356" ht="64" customHeight="1">
       <c r="A356" s="20" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="F356" s="20" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
           <t>노벨상 받은 쑥, 비타민 풍부,진정</t>
         </is>
       </c>
-      <c r="F357" s="20" t="n"/>
+      <c r="F357" s="20" t="inlineStr"/>
     </row>
     <row r="358" ht="48" customHeight="1">
       <c r="A358" s="20" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="F358" s="20" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="F360" s="20" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -15111,7 +15111,7 @@
           <t>진정</t>
         </is>
       </c>
-      <c r="F372" s="10" t="n"/>
+      <c r="F372" s="10" t="inlineStr"/>
     </row>
     <row r="373" ht="80" customHeight="1">
       <c r="A373" s="10" t="inlineStr">
@@ -15132,10 +15132,10 @@
       </c>
       <c r="E373" s="10" t="inlineStr">
         <is>
-          <t>포타슘 코코 글리시네이트 / 음이온, 코코넛오일, 아미노산을 / 이용한 순하고 부드러움, / 어독성이 낮고 생분해성이 우수, pH 7~9</t>
-        </is>
-      </c>
-      <c r="F373" s="10" t="n"/>
+          <t>포타슘 코코 글리시네이트 · 음이온, 코코넛오일, 아미노산을 · 이용한 순하고 부드러움 · 어독성이 낮고 생분해성이 우수, pH 7~9</t>
+        </is>
+      </c>
+      <c r="F373" s="10" t="inlineStr"/>
     </row>
     <row r="374" ht="16" customHeight="1">
       <c r="A374" s="10" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="F375" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="F376" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -15379,10 +15379,10 @@
       </c>
       <c r="E386" s="20" t="inlineStr">
         <is>
-          <t>고농축 캐모마일 추출물 함유, / 가벼움 사용감과 퍼짐성</t>
-        </is>
-      </c>
-      <c r="F386" s="20" t="n"/>
+          <t>고농축 캐모마일 추출물 함유 · 가벼움 사용감과 퍼짐성</t>
+        </is>
+      </c>
+      <c r="F386" s="20" t="inlineStr"/>
     </row>
     <row r="387" ht="32" customHeight="1">
       <c r="A387" s="20" t="inlineStr">
@@ -15407,10 +15407,10 @@
       </c>
       <c r="E387" s="20" t="inlineStr">
         <is>
-          <t>층분리 현상 방지, / 물에 잘 씻길 수 있도록 도와줌</t>
-        </is>
-      </c>
-      <c r="F387" s="20" t="n"/>
+          <t>층분리 현상 방지 · 물에 잘 씻길 수 있도록 도와줌</t>
+        </is>
+      </c>
+      <c r="F387" s="20" t="inlineStr"/>
     </row>
     <row r="388" ht="32" customHeight="1">
       <c r="A388" s="20" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="E397" s="10" t="inlineStr">
         <is>
-          <t>사과주스로 만든 물비누 / 저자극, 생분해, 음이온</t>
+          <t>사과주스로 만든 물비누 · 저자극, 생분해, 음이온</t>
         </is>
       </c>
       <c r="F397" s="10" t="inlineStr">
@@ -15633,16 +15633,16 @@
       </c>
       <c r="E398" s="10" t="inlineStr">
         <is>
-          <t>사탕무(보습)에서 추출한 당+코코넛오일로 / 만든 양쪽성 계면활성제</t>
+          <t>사탕무(보습)에서 추출한 당+코코넛오일로 · 만든 양쪽성 계면활성제</t>
         </is>
       </c>
       <c r="F398" s="10" t="inlineStr">
         <is>
-          <t>애플 / 계면활성제</t>
-        </is>
-      </c>
-    </row>
-    <row r="399" ht="32" customHeight="1">
+          <t>애플 · 계면활성제</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" ht="16" customHeight="1">
       <c r="A399" s="10" t="inlineStr">
         <is>
           <t>개똥쑥추출물</t>
@@ -15665,10 +15665,10 @@
       </c>
       <c r="E399" s="10" t="inlineStr">
         <is>
-          <t>노벨상 받은 쑥, / 항산화, 진정</t>
-        </is>
-      </c>
-      <c r="F399" s="10" t="n"/>
+          <t>노벨상 받은 쑥 · 항산화, 진정</t>
+        </is>
+      </c>
+      <c r="F399" s="10" t="inlineStr"/>
     </row>
     <row r="400" ht="48" customHeight="1">
       <c r="A400" s="10" t="inlineStr">
@@ -15698,7 +15698,7 @@
       </c>
       <c r="F400" s="10" t="inlineStr">
         <is>
-          <t>비피다발효용해물, / 사카로미세스발효여과물</t>
+          <t>비피다발효용해물 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="F402" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -16233,10 +16233,10 @@
       </c>
       <c r="E426" s="10" t="inlineStr">
         <is>
-          <t>천연 순한 세정성분(애플계면활성제, 데실/라우릴 글루코이드) 으로 구성. 풍성한 거품, / 사용 후 촉촉함, 약산성</t>
-        </is>
-      </c>
-      <c r="F426" s="10" t="n"/>
+          <t>천연 순한 세정성분(애플계면활성제, 데실 · 라우릴 글루코이드) 으로 구성. 풍성한 거품 · 사용 후 촉촉함, 약산성</t>
+        </is>
+      </c>
+      <c r="F426" s="10" t="inlineStr"/>
     </row>
     <row r="427" ht="64" customHeight="1">
       <c r="A427" s="10" t="inlineStr">
@@ -16261,12 +16261,12 @@
       </c>
       <c r="E427" s="10" t="inlineStr">
         <is>
-          <t>7가지 유기농 채소 복합추출물. / 저온 추출법을 이용하여 비타민의 파괴를 최소화시켜 추출한 원료. 피부건강증진</t>
+          <t>7가지 유기농 채소 복합추출물. · 저온 추출법을 이용하여 비타민의 파괴를 최소화시켜 추출한 원료. 피부건강증진</t>
         </is>
       </c>
       <c r="F427" s="10" t="inlineStr">
         <is>
-          <t>유기농 / 브라이트닝 / 솔루션</t>
+          <t>유기농 · 브라이트닝 · 솔루션</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="F428" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -16325,12 +16325,12 @@
       </c>
       <c r="E429" s="10" t="inlineStr">
         <is>
-          <t>300g 맞춤. 로즈제라늄, 로즈워더 등 / 가용화제 그리고 보존제 처방.</t>
+          <t>300g 맞춤. 로즈제라늄, 로즈워더 등 · 가용화제 그리고 보존제 처방.</t>
         </is>
       </c>
       <c r="F429" s="10" t="inlineStr">
         <is>
-          <t>피부타입에 / 맞는 아로마수 선택 / 오렌지 플라워, 로맨틱 레몬, 그린 프레쉬 등</t>
+          <t>피부타입에 · 맞는 아로마수 선택 · 오렌지 플라워, 로맨틱 레몬, 그린 프레쉬 등</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="E439" s="20" t="inlineStr">
         <is>
-          <t>사과주스로 만든 물비누 / 저자극, 생분해.음이온계면활성제</t>
+          <t>사과주스로 만든 물비누 · 저자극, 생분해.음이온계면활성제</t>
         </is>
       </c>
       <c r="F439" s="20" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="F443" s="20" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -16798,10 +16798,10 @@
       </c>
       <c r="E453" s="10" t="inlineStr">
         <is>
-          <t>고농축 카렌듈라꽃 추출물 함유, / 올레인산과 비타민A성분 풍부</t>
-        </is>
-      </c>
-      <c r="F453" s="10" t="n"/>
+          <t>고농축 카렌듈라꽃 추출물 함유 · 올레인산과 비타민A성분 풍부</t>
+        </is>
+      </c>
+      <c r="F453" s="10" t="inlineStr"/>
     </row>
     <row r="454" ht="32" customHeight="1">
       <c r="A454" s="10" t="inlineStr">
@@ -16826,10 +16826,10 @@
       </c>
       <c r="E454" s="10" t="inlineStr">
         <is>
-          <t>층분리 현상 방지, / 물에 잘 씻길 수 있도록 도와줌</t>
-        </is>
-      </c>
-      <c r="F454" s="10" t="n"/>
+          <t>층분리 현상 방지 · 물에 잘 씻길 수 있도록 도와줌</t>
+        </is>
+      </c>
+      <c r="F454" s="10" t="inlineStr"/>
     </row>
     <row r="455" ht="32" customHeight="1">
       <c r="A455" s="10" t="inlineStr">
@@ -17042,12 +17042,12 @@
       </c>
       <c r="E465" s="20" t="inlineStr">
         <is>
-          <t>올리브오일유래. / 물과 오일 분리저지</t>
+          <t>올리브오일유래. · 물과 오일 분리저지</t>
         </is>
       </c>
       <c r="F465" s="20" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -17106,7 +17106,7 @@
       </c>
       <c r="E467" s="20" t="inlineStr">
         <is>
-          <t>자몽씨추출물, 황금추출물 등 / 복합 균번식억제.</t>
+          <t>자몽씨추출물, 황금추출물 등 · 복합 균번식억제.</t>
         </is>
       </c>
       <c r="F467" s="20" t="inlineStr">
@@ -17175,7 +17175,7 @@
       </c>
       <c r="F469" s="20" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -17419,12 +17419,12 @@
       </c>
       <c r="E481" s="10" t="inlineStr">
         <is>
-          <t>올리브오일유래. / 물과 오일 분리저지</t>
+          <t>올리브오일유래. · 물과 오일 분리저지</t>
         </is>
       </c>
       <c r="F481" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -17483,7 +17483,7 @@
       </c>
       <c r="E483" s="10" t="inlineStr">
         <is>
-          <t>자몽씨추출물, 황금추출물 등 / 복합 균번식억제.</t>
+          <t>자몽씨추출물, 황금추출물 등 · 복합 균번식억제.</t>
         </is>
       </c>
       <c r="F483" s="10" t="inlineStr">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="F484" s="10" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F500" s="20" t="inlineStr">
         <is>
-          <t>레몬에센셜오일 등 / 원하는 에센셜오일</t>
+          <t>레몬에센셜오일 등 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -18057,7 +18057,7 @@
       </c>
       <c r="E509" s="10" t="inlineStr">
         <is>
-          <t>사과주스로 만든 물비누, / 생분해OK, 피부자극최소, 풍부한 거품OK</t>
+          <t>사과주스로 만든 물비누 · 생분해OK, 피부자극최소, 풍부한 거품OK</t>
         </is>
       </c>
       <c r="F509" s="10" t="inlineStr">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="E510" s="10" t="inlineStr">
         <is>
-          <t>편백 잎을 수증기추출, 피톤치드 함유, 수분공급,</t>
+          <t>편백 잎을 수증기추출, 피톤치드 함유, 수분공급</t>
         </is>
       </c>
       <c r="F510" s="10" t="inlineStr">
@@ -18158,7 +18158,7 @@
       </c>
       <c r="F512" s="10" t="inlineStr">
         <is>
-          <t>오가닉 7 솔루션, / 유기농 프레쉬 5 솔루션</t>
+          <t>오가닉 7 솔루션 · 유기농 프레쉬 5 솔루션</t>
         </is>
       </c>
     </row>
@@ -18185,12 +18185,12 @@
       </c>
       <c r="E513" s="10" t="inlineStr">
         <is>
-          <t>정밀 저울을 이용하세요. 컴프리뿌리, / 100%알란토인, 진정, 트러블피부관리 / 분말의 경우 0.3%가 넘으면 다 녹지 않고 침전됩니다. / 뿌옇게..^^</t>
+          <t>정밀 저울을 이용하세요. 컴프리뿌리 · 100%알란토인, 진정, 트러블피부관리 · 분말의 경우 0.3%가 넘으면 다 녹지 않고 침전됩니다. · 뿌옇게..^^</t>
         </is>
       </c>
       <c r="F513" s="10" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -18222,7 +18222,7 @@
       </c>
       <c r="F514" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올3g / (편백터의 양을 49g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올3g · (편백터의 양을 49g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -18397,7 +18397,7 @@
       </c>
       <c r="E524" s="20" t="inlineStr">
         <is>
-          <t>올레인산 풍부, / 비타민E, 폴리페놀 등 항산화 성분</t>
+          <t>올레인산 풍부 · 비타민E, 폴리페놀 등 항산화 성분</t>
         </is>
       </c>
       <c r="F524" s="20" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="F525" s="20" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -18486,7 +18486,7 @@
       </c>
       <c r="F527" s="20" t="inlineStr">
         <is>
-          <t>원하는 / 추출물</t>
+          <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
@@ -18509,12 +18509,12 @@
       </c>
       <c r="E528" s="20" t="inlineStr">
         <is>
-          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 / 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
+          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 · 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
         </is>
       </c>
       <c r="F528" s="20" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="E529" s="20" t="inlineStr">
         <is>
-          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
+          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
       <c r="F529" s="20" t="inlineStr">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="F530" s="20" t="inlineStr">
         <is>
-          <t>레몬에센셜오일 등 / 원하는 에센셜오일</t>
+          <t>레몬에센셜오일 등 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -18927,12 +18927,12 @@
       </c>
       <c r="E550" s="20" t="inlineStr">
         <is>
-          <t>사탕무(보습)에서 추출한 당+코코넛오일 로 / 만든 양쪽성 계면활성제</t>
+          <t>사탕무(보습)에서 추출한 당+코코넛오일 로 · 만든 양쪽성 계면활성제</t>
         </is>
       </c>
       <c r="F550" s="20" t="inlineStr">
         <is>
-          <t>애플 / 계면활성제</t>
+          <t>애플 · 계면활성제</t>
         </is>
       </c>
     </row>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="E551" s="20" t="inlineStr">
         <is>
-          <t>음이온 계면활성제, 거품, 세정력,</t>
+          <t>음이온 계면활성제, 거품, 세정력</t>
         </is>
       </c>
       <c r="F551" s="20" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="F553" s="20" t="inlineStr">
         <is>
-          <t>아카시아콜라겐, / 플라센타 등</t>
+          <t>아카시아콜라겐 · 플라센타 등</t>
         </is>
       </c>
     </row>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="F554" s="20" t="inlineStr">
         <is>
-          <t>아카시아 / 콜라겐, 콜라겐</t>
+          <t>아카시아 · 콜라겐, 콜라겐</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="E555" s="20" t="inlineStr">
         <is>
-          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
+          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
       <c r="F555" s="20" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="F556" s="20" t="inlineStr">
         <is>
-          <t>로즈제라늄 / 에센셜오일</t>
+          <t>로즈제라늄 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -19222,12 +19222,12 @@
       </c>
       <c r="E564" s="10" t="inlineStr">
         <is>
-          <t>사탕무(보습)에서 추출한 당+코코넛오일 로 / 만든 양쪽성 계면활성제</t>
+          <t>사탕무(보습)에서 추출한 당+코코넛오일 로 · 만든 양쪽성 계면활성제</t>
         </is>
       </c>
       <c r="F564" s="10" t="inlineStr">
         <is>
-          <t>애플 / 계면활성제</t>
+          <t>애플 · 계면활성제</t>
         </is>
       </c>
     </row>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="E565" s="10" t="inlineStr">
         <is>
-          <t>음이온 계면활성제, 거품, 세정력,</t>
+          <t>음이온 계면활성제, 거품, 세정력</t>
         </is>
       </c>
       <c r="F565" s="10" t="inlineStr">
@@ -19306,12 +19306,12 @@
       </c>
       <c r="E567" s="10" t="inlineStr">
         <is>
-          <t>금잔화추출물, / 민감 트러블완화.</t>
+          <t>금잔화추출물 · 민감 트러블완화.</t>
         </is>
       </c>
       <c r="F567" s="10" t="inlineStr">
         <is>
-          <t>알란토인, / 감초추출물</t>
+          <t>알란토인 · 감초추출물</t>
         </is>
       </c>
     </row>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="E568" s="10" t="inlineStr">
         <is>
-          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
+          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
       <c r="F568" s="10" t="inlineStr">
@@ -19462,7 +19462,7 @@
       </c>
       <c r="E575" s="20" t="inlineStr">
         <is>
-          <t>올레인산 풍부, / 비타민E, 폴리페놀 등 항산화 성분</t>
+          <t>올레인산 풍부 · 비타민E, 폴리페놀 등 항산화 성분</t>
         </is>
       </c>
       <c r="F575" s="20" t="inlineStr">
@@ -19494,10 +19494,10 @@
       </c>
       <c r="E576" s="20" t="inlineStr">
         <is>
-          <t>층분리 현상 방지, / 물에 잘 씻길 수 있도록 도와줌</t>
-        </is>
-      </c>
-      <c r="F576" s="20" t="n"/>
+          <t>층분리 현상 방지 · 물에 잘 씻길 수 있도록 도와줌</t>
+        </is>
+      </c>
+      <c r="F576" s="20" t="inlineStr"/>
     </row>
     <row r="577" ht="14" customHeight="1">
       <c r="A577" s="15" t="inlineStr">
@@ -19650,7 +19650,7 @@
       </c>
       <c r="F585" s="10" t="inlineStr">
         <is>
-          <t>포도씨오일, / 해바라기오일, 아몬드오일 등 / 가벼운 오일</t>
+          <t>포도씨오일 · 해바라기오일, 아몬드오일 등 · 가벼운 오일</t>
         </is>
       </c>
     </row>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="F587" s="10" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="E588" s="10" t="inlineStr">
         <is>
-          <t>시더우드 잎을 수증기 추출법으로 추출, / 지루성 두피관리, / 항균, 비듬균 강력한 효과 / (허브누리 실험보고서 참고)</t>
+          <t>시더우드 잎을 수증기 추출법으로 추출 · 지루성 두피관리 · 항균, 비듬균 강력한 효과 · (허브누리 실험보고서 참고)</t>
         </is>
       </c>
       <c r="F588" s="10" t="inlineStr">
@@ -19875,12 +19875,12 @@
       </c>
       <c r="E597" s="20" t="inlineStr">
         <is>
-          <t>보성 무농약 녹차, / 식물성 에탄올에 저온추출, 감압농축, 동결건조하여 유효성분을 많이 포함하고 있습니다. 폴리페놀 함량이 3배높고 항산화 작용</t>
+          <t>보성 무농약 녹차 · 식물성 에탄올에 저온추출, 감압농축, 동결건조하여 유효성분을 많이 포함하고 있습니다. 폴리페놀 함량이 3배높고 항산화 작용</t>
         </is>
       </c>
       <c r="F597" s="20" t="inlineStr">
         <is>
-          <t>녹소초 추출물, / 유기농 브라이트닝 5 등.</t>
+          <t>녹소초 추출물 · 유기농 브라이트닝 5 등.</t>
         </is>
       </c>
     </row>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="E598" s="20" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F598" s="20" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="E599" s="20" t="inlineStr">
         <is>
-          <t>월견초 종자유, / 감마리놀린산 다량함유,</t>
+          <t>월견초 종자유 · 감마리놀린산 다량함유</t>
         </is>
       </c>
       <c r="F599" s="20" t="inlineStr">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="F602" s="20" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -20151,10 +20151,10 @@
       </c>
       <c r="E609" s="10" t="inlineStr">
         <is>
-          <t>옥수수전분으로 만든 점증제. 물에 녹이기 위해서는 가열과정이 필요합니다. / 이 원료만 빼면 거품용기에 넣어서 사용하셔도 됩니다.</t>
-        </is>
-      </c>
-      <c r="F609" s="10" t="n"/>
+          <t>옥수수전분으로 만든 점증제. 물에 녹이기 위해서는 가열과정이 필요합니다. · 이 원료만 빼면 거품용기에 넣어서 사용하셔도 됩니다.</t>
+        </is>
+      </c>
+      <c r="F609" s="10" t="inlineStr"/>
     </row>
     <row r="610" ht="112" customHeight="1">
       <c r="A610" s="10" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="F612" s="10" t="inlineStr">
         <is>
-          <t>유기농 / 브라이트닝 / 솔루션</t>
+          <t>유기농 · 브라이트닝 · 솔루션</t>
         </is>
       </c>
     </row>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="F614" s="10" t="inlineStr">
         <is>
-          <t>천연한방 / 보존제</t>
+          <t>천연한방 · 보존제</t>
         </is>
       </c>
     </row>
@@ -20344,7 +20344,7 @@
       </c>
       <c r="F615" s="10" t="inlineStr">
         <is>
-          <t>스윗오렌지 / 에센셜오일 등</t>
+          <t>스윗오렌지 · 에센셜오일 등</t>
         </is>
       </c>
     </row>
@@ -20507,7 +20507,7 @@
       </c>
       <c r="E625" s="20" t="inlineStr">
         <is>
-          <t>피부에 자연적으로 존재하는 성분, / 피부결 개선, 보습 / 장벽 강화, 우수한 흡수력</t>
+          <t>피부에 자연적으로 존재하는 성분 · 피부결 개선, 보습 · 장벽 강화, 우수한 흡수력</t>
         </is>
       </c>
       <c r="F625" s="20" t="inlineStr">
@@ -20539,10 +20539,10 @@
       </c>
       <c r="E626" s="20" t="inlineStr">
         <is>
-          <t>세틸알코올+지방산 유도체를 반응시켜 만든 에스테르오일, / 끈적임이 없고 가볍고 산뜻한 사용감</t>
-        </is>
-      </c>
-      <c r="F626" s="20" t="n"/>
+          <t>세틸알코올+지방산 유도체를 반응시켜 만든 에스테르오일 · 끈적임이 없고 가볍고 산뜻한 사용감</t>
+        </is>
+      </c>
+      <c r="F626" s="20" t="inlineStr"/>
     </row>
     <row r="627" ht="32" customHeight="1">
       <c r="A627" s="20" t="inlineStr">
@@ -20567,10 +20567,10 @@
       </c>
       <c r="E627" s="20" t="inlineStr">
         <is>
-          <t>층분리 현상 방지, / 물에 잘 씻길 수 있도록 도와줌</t>
-        </is>
-      </c>
-      <c r="F627" s="20" t="n"/>
+          <t>층분리 현상 방지 · 물에 잘 씻길 수 있도록 도와줌</t>
+        </is>
+      </c>
+      <c r="F627" s="20" t="inlineStr"/>
     </row>
     <row r="628" ht="32" customHeight="1">
       <c r="A628" s="20" t="inlineStr">
@@ -20595,7 +20595,7 @@
       </c>
       <c r="E628" s="20" t="inlineStr">
         <is>
-          <t>레몬, 레몬그라스, 로즈우드 / 에센셜오일 블렌딩</t>
+          <t>레몬, 레몬그라스, 로즈우드 · 에센셜오일 블렌딩</t>
         </is>
       </c>
       <c r="F628" s="20" t="inlineStr">
@@ -20822,7 +20822,7 @@
       </c>
       <c r="F639" s="10" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -20852,7 +20852,7 @@
           <t>가용화제</t>
         </is>
       </c>
-      <c r="F640" s="10" t="n"/>
+      <c r="F640" s="10" t="inlineStr"/>
     </row>
     <row r="641" ht="32" customHeight="1">
       <c r="A641" s="10" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="E641" s="10" t="inlineStr">
         <is>
-          <t>비타민 B3, / 식약처 기능성 고시원료</t>
+          <t>비타민 B3 · 식약처 기능성 고시원료</t>
         </is>
       </c>
       <c r="F641" s="10" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="F642" s="10" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -20946,7 +20946,7 @@
       </c>
       <c r="F643" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
